--- a/CopadoMundoFIFA2026_DadosPowerBI.xlsx
+++ b/CopadoMundoFIFA2026_DadosPowerBI.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30327"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8435351A-C16F-4EAD-8562-4B2E8EA9F9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9018FC1F-37E8-48A7-AE67-7BE5CF9C2266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="4" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DimSelecao" sheetId="1" r:id="rId1"/>
@@ -4132,7 +4132,9 @@
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="8"/>
+      <c r="A57" s="8">
+        <v>56</v>
+      </c>
       <c r="B57" s="7" t="s">
         <v>124</v>
       </c>
@@ -4141,7 +4143,9 @@
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="8"/>
+      <c r="A58" s="8">
+        <v>57</v>
+      </c>
       <c r="B58" s="7" t="s">
         <v>125</v>
       </c>
@@ -4150,7 +4154,9 @@
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="8"/>
+      <c r="A59" s="8">
+        <v>58</v>
+      </c>
       <c r="B59" s="7" t="s">
         <v>126</v>
       </c>
@@ -4159,7 +4165,9 @@
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="8"/>
+      <c r="A60" s="8">
+        <v>59</v>
+      </c>
       <c r="B60" s="7" t="s">
         <v>127</v>
       </c>
@@ -4168,7 +4176,9 @@
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="8"/>
+      <c r="A61" s="8">
+        <v>60</v>
+      </c>
       <c r="B61" s="7" t="s">
         <v>128</v>
       </c>
@@ -4177,7 +4187,9 @@
       </c>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="8"/>
+      <c r="A62" s="8">
+        <v>61</v>
+      </c>
       <c r="B62" s="7" t="s">
         <v>129</v>
       </c>
@@ -4186,7 +4198,9 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="8"/>
+      <c r="A63" s="8">
+        <v>62</v>
+      </c>
       <c r="B63" s="7" t="s">
         <v>130</v>
       </c>
@@ -4195,7 +4209,9 @@
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="8"/>
+      <c r="A64" s="8">
+        <v>63</v>
+      </c>
       <c r="B64" s="7" t="s">
         <v>131</v>
       </c>
@@ -4204,7 +4220,9 @@
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="8"/>
+      <c r="A65" s="8">
+        <v>64</v>
+      </c>
       <c r="B65" s="7" t="s">
         <v>132</v>
       </c>
@@ -4213,7 +4231,9 @@
       </c>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="8"/>
+      <c r="A66" s="8">
+        <v>65</v>
+      </c>
       <c r="B66" s="7" t="s">
         <v>133</v>
       </c>
@@ -4222,7 +4242,9 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="8"/>
+      <c r="A67" s="8">
+        <v>66</v>
+      </c>
       <c r="B67" s="7" t="s">
         <v>134</v>
       </c>
@@ -4231,7 +4253,9 @@
       </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="8"/>
+      <c r="A68" s="8">
+        <v>67</v>
+      </c>
       <c r="B68" s="7" t="s">
         <v>135</v>
       </c>
@@ -4240,7 +4264,9 @@
       </c>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="8"/>
+      <c r="A69" s="8">
+        <v>68</v>
+      </c>
       <c r="B69" s="7" t="s">
         <v>136</v>
       </c>
@@ -4249,7 +4275,9 @@
       </c>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="8"/>
+      <c r="A70" s="8">
+        <v>69</v>
+      </c>
       <c r="B70" s="7" t="s">
         <v>137</v>
       </c>
@@ -4258,7 +4286,9 @@
       </c>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="8"/>
+      <c r="A71" s="8">
+        <v>70</v>
+      </c>
       <c r="B71" s="7" t="s">
         <v>138</v>
       </c>
@@ -4267,7 +4297,9 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="8"/>
+      <c r="A72" s="8">
+        <v>71</v>
+      </c>
       <c r="B72" s="7" t="s">
         <v>139</v>
       </c>
@@ -4276,7 +4308,9 @@
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="8"/>
+      <c r="A73" s="8">
+        <v>72</v>
+      </c>
       <c r="B73" s="7" t="s">
         <v>140</v>
       </c>
@@ -4285,7 +4319,9 @@
       </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="8"/>
+      <c r="A74" s="8">
+        <v>73</v>
+      </c>
       <c r="B74" s="7" t="s">
         <v>141</v>
       </c>
@@ -4294,7 +4330,9 @@
       </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="8"/>
+      <c r="A75" s="8">
+        <v>74</v>
+      </c>
       <c r="B75" s="7" t="s">
         <v>142</v>
       </c>
@@ -4303,7 +4341,9 @@
       </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="8"/>
+      <c r="A76" s="8">
+        <v>75</v>
+      </c>
       <c r="B76" s="7" t="s">
         <v>143</v>
       </c>
@@ -4312,7 +4352,9 @@
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="8"/>
+      <c r="A77" s="8">
+        <v>76</v>
+      </c>
       <c r="B77" s="7" t="s">
         <v>144</v>
       </c>
@@ -4321,7 +4363,9 @@
       </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="8"/>
+      <c r="A78" s="8">
+        <v>77</v>
+      </c>
       <c r="B78" s="7" t="s">
         <v>145</v>
       </c>
@@ -4330,7 +4374,9 @@
       </c>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="8"/>
+      <c r="A79" s="8">
+        <v>78</v>
+      </c>
       <c r="B79" s="7" t="s">
         <v>146</v>
       </c>
@@ -4339,7 +4385,9 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="8"/>
+      <c r="A80" s="8">
+        <v>79</v>
+      </c>
       <c r="B80" s="7" t="s">
         <v>147</v>
       </c>
@@ -4348,7 +4396,9 @@
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="8"/>
+      <c r="A81" s="8">
+        <v>80</v>
+      </c>
       <c r="B81" s="7" t="s">
         <v>148</v>
       </c>
@@ -4357,7 +4407,9 @@
       </c>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="8"/>
+      <c r="A82" s="8">
+        <v>81</v>
+      </c>
       <c r="B82" s="7" t="s">
         <v>149</v>
       </c>
@@ -4366,7 +4418,9 @@
       </c>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="8"/>
+      <c r="A83" s="8">
+        <v>82</v>
+      </c>
       <c r="B83" s="7" t="s">
         <v>150</v>
       </c>
@@ -4375,7 +4429,9 @@
       </c>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="8"/>
+      <c r="A84" s="8">
+        <v>83</v>
+      </c>
       <c r="B84" s="7" t="s">
         <v>151</v>
       </c>
@@ -4384,7 +4440,9 @@
       </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="8"/>
+      <c r="A85" s="8">
+        <v>84</v>
+      </c>
       <c r="B85" s="7" t="s">
         <v>152</v>
       </c>
@@ -4393,7 +4451,9 @@
       </c>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="8"/>
+      <c r="A86" s="8">
+        <v>85</v>
+      </c>
       <c r="B86" s="7" t="s">
         <v>153</v>
       </c>
@@ -4402,7 +4462,9 @@
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="8"/>
+      <c r="A87" s="8">
+        <v>86</v>
+      </c>
       <c r="B87" s="7" t="s">
         <v>154</v>
       </c>
@@ -4411,7 +4473,9 @@
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="8"/>
+      <c r="A88" s="8">
+        <v>87</v>
+      </c>
       <c r="B88" s="7" t="s">
         <v>155</v>
       </c>
@@ -4420,7 +4484,9 @@
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="8"/>
+      <c r="A89" s="8">
+        <v>88</v>
+      </c>
       <c r="B89" s="7" t="s">
         <v>156</v>
       </c>
@@ -4429,7 +4495,9 @@
       </c>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="8"/>
+      <c r="A90" s="8">
+        <v>89</v>
+      </c>
       <c r="B90" s="7" t="s">
         <v>157</v>
       </c>
@@ -4438,7 +4506,9 @@
       </c>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="8"/>
+      <c r="A91" s="8">
+        <v>90</v>
+      </c>
       <c r="B91" s="7" t="s">
         <v>158</v>
       </c>
@@ -4447,7 +4517,9 @@
       </c>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="8"/>
+      <c r="A92" s="8">
+        <v>91</v>
+      </c>
       <c r="B92" s="7" t="s">
         <v>159</v>
       </c>
@@ -4456,7 +4528,9 @@
       </c>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="8"/>
+      <c r="A93" s="8">
+        <v>92</v>
+      </c>
       <c r="B93" s="7" t="s">
         <v>160</v>
       </c>
@@ -4465,7 +4539,9 @@
       </c>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="8"/>
+      <c r="A94" s="8">
+        <v>93</v>
+      </c>
       <c r="B94" s="7" t="s">
         <v>161</v>
       </c>
@@ -4474,7 +4550,9 @@
       </c>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="8"/>
+      <c r="A95" s="8">
+        <v>94</v>
+      </c>
       <c r="B95" s="7" t="s">
         <v>162</v>
       </c>
@@ -4483,7 +4561,9 @@
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="8"/>
+      <c r="A96" s="8">
+        <v>95</v>
+      </c>
       <c r="B96" s="7" t="s">
         <v>163</v>
       </c>
@@ -4492,7 +4572,9 @@
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="8"/>
+      <c r="A97" s="8">
+        <v>96</v>
+      </c>
       <c r="B97" s="7" t="s">
         <v>164</v>
       </c>
@@ -4501,7 +4583,9 @@
       </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="8"/>
+      <c r="A98" s="8">
+        <v>97</v>
+      </c>
       <c r="B98" s="7" t="s">
         <v>165</v>
       </c>
@@ -4510,7 +4594,9 @@
       </c>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="8"/>
+      <c r="A99" s="8">
+        <v>98</v>
+      </c>
       <c r="B99" s="7" t="s">
         <v>166</v>
       </c>
@@ -4519,7 +4605,9 @@
       </c>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="8"/>
+      <c r="A100" s="8">
+        <v>99</v>
+      </c>
       <c r="B100" s="7" t="s">
         <v>167</v>
       </c>
@@ -4528,7 +4616,9 @@
       </c>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="8"/>
+      <c r="A101" s="8">
+        <v>100</v>
+      </c>
       <c r="B101" s="7" t="s">
         <v>168</v>
       </c>
@@ -4537,7 +4627,9 @@
       </c>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="8"/>
+      <c r="A102" s="8">
+        <v>101</v>
+      </c>
       <c r="B102" s="7" t="s">
         <v>169</v>
       </c>
@@ -4546,7 +4638,9 @@
       </c>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="8"/>
+      <c r="A103" s="8">
+        <v>102</v>
+      </c>
       <c r="B103" s="7" t="s">
         <v>170</v>
       </c>
@@ -4555,7 +4649,9 @@
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="8"/>
+      <c r="A104" s="8">
+        <v>103</v>
+      </c>
       <c r="B104" s="7" t="s">
         <v>171</v>
       </c>
@@ -4564,7 +4660,9 @@
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="8"/>
+      <c r="A105" s="8">
+        <v>104</v>
+      </c>
       <c r="B105" s="7" t="s">
         <v>172</v>
       </c>
@@ -4573,7 +4671,9 @@
       </c>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106" s="8"/>
+      <c r="A106" s="8">
+        <v>105</v>
+      </c>
       <c r="B106" s="7" t="s">
         <v>173</v>
       </c>
@@ -4582,7 +4682,9 @@
       </c>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="8"/>
+      <c r="A107" s="8">
+        <v>106</v>
+      </c>
       <c r="B107" s="7" t="s">
         <v>174</v>
       </c>
@@ -4591,7 +4693,9 @@
       </c>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="8"/>
+      <c r="A108" s="8">
+        <v>107</v>
+      </c>
       <c r="B108" s="7" t="s">
         <v>175</v>
       </c>
@@ -4600,7 +4704,9 @@
       </c>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="8"/>
+      <c r="A109" s="8">
+        <v>108</v>
+      </c>
       <c r="B109" s="7" t="s">
         <v>176</v>
       </c>
@@ -4609,7 +4715,9 @@
       </c>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" s="8"/>
+      <c r="A110" s="8">
+        <v>109</v>
+      </c>
       <c r="B110" s="7" t="s">
         <v>177</v>
       </c>
@@ -4618,7 +4726,9 @@
       </c>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="8"/>
+      <c r="A111" s="8">
+        <v>110</v>
+      </c>
       <c r="B111" s="7" t="s">
         <v>178</v>
       </c>
@@ -4627,7 +4737,9 @@
       </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="8"/>
+      <c r="A112" s="8">
+        <v>111</v>
+      </c>
       <c r="B112" s="7" t="s">
         <v>179</v>
       </c>
@@ -4636,7 +4748,9 @@
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="8"/>
+      <c r="A113" s="8">
+        <v>112</v>
+      </c>
       <c r="B113" s="7" t="s">
         <v>180</v>
       </c>
@@ -4645,7 +4759,9 @@
       </c>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="8"/>
+      <c r="A114" s="8">
+        <v>113</v>
+      </c>
       <c r="B114" s="7" t="s">
         <v>181</v>
       </c>
@@ -4654,7 +4770,9 @@
       </c>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="8"/>
+      <c r="A115" s="8">
+        <v>114</v>
+      </c>
       <c r="B115" s="7" t="s">
         <v>182</v>
       </c>
@@ -4663,7 +4781,9 @@
       </c>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="8"/>
+      <c r="A116" s="8">
+        <v>115</v>
+      </c>
       <c r="B116" s="7" t="s">
         <v>183</v>
       </c>
@@ -4672,7 +4792,9 @@
       </c>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="8"/>
+      <c r="A117" s="8">
+        <v>116</v>
+      </c>
       <c r="B117" s="7" t="s">
         <v>184</v>
       </c>
@@ -4681,7 +4803,9 @@
       </c>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="8"/>
+      <c r="A118" s="8">
+        <v>117</v>
+      </c>
       <c r="B118" s="7" t="s">
         <v>185</v>
       </c>
@@ -4690,7 +4814,9 @@
       </c>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="8"/>
+      <c r="A119" s="8">
+        <v>118</v>
+      </c>
       <c r="B119" s="7" t="s">
         <v>186</v>
       </c>
@@ -4699,7 +4825,9 @@
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="8"/>
+      <c r="A120" s="8">
+        <v>119</v>
+      </c>
       <c r="B120" s="7" t="s">
         <v>187</v>
       </c>
@@ -4708,7 +4836,9 @@
       </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="8"/>
+      <c r="A121" s="8">
+        <v>120</v>
+      </c>
       <c r="B121" s="7" t="s">
         <v>188</v>
       </c>
@@ -4717,7 +4847,9 @@
       </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="8"/>
+      <c r="A122" s="8">
+        <v>121</v>
+      </c>
       <c r="B122" s="7" t="s">
         <v>189</v>
       </c>
@@ -4726,7 +4858,9 @@
       </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="8"/>
+      <c r="A123" s="8">
+        <v>122</v>
+      </c>
       <c r="B123" s="7" t="s">
         <v>190</v>
       </c>
@@ -4735,7 +4869,9 @@
       </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="8"/>
+      <c r="A124" s="8">
+        <v>123</v>
+      </c>
       <c r="B124" s="7" t="s">
         <v>191</v>
       </c>
@@ -4744,7 +4880,9 @@
       </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="8"/>
+      <c r="A125" s="8">
+        <v>124</v>
+      </c>
       <c r="B125" s="7" t="s">
         <v>192</v>
       </c>
@@ -4753,7 +4891,9 @@
       </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="8"/>
+      <c r="A126" s="8">
+        <v>125</v>
+      </c>
       <c r="B126" s="7" t="s">
         <v>193</v>
       </c>
@@ -4762,7 +4902,9 @@
       </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="8"/>
+      <c r="A127" s="8">
+        <v>126</v>
+      </c>
       <c r="B127" s="7" t="s">
         <v>194</v>
       </c>
@@ -4771,7 +4913,9 @@
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="8"/>
+      <c r="A128" s="8">
+        <v>127</v>
+      </c>
       <c r="B128" s="7" t="s">
         <v>195</v>
       </c>
@@ -4780,7 +4924,9 @@
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="8"/>
+      <c r="A129" s="8">
+        <v>128</v>
+      </c>
       <c r="B129" s="7" t="s">
         <v>196</v>
       </c>
@@ -4789,7 +4935,9 @@
       </c>
     </row>
     <row r="130" spans="1:3">
-      <c r="A130" s="8"/>
+      <c r="A130" s="8">
+        <v>129</v>
+      </c>
       <c r="B130" s="7" t="s">
         <v>197</v>
       </c>
@@ -4798,7 +4946,9 @@
       </c>
     </row>
     <row r="131" spans="1:3">
-      <c r="A131" s="8"/>
+      <c r="A131" s="8">
+        <v>130</v>
+      </c>
       <c r="B131" s="7" t="s">
         <v>198</v>
       </c>
@@ -4807,7 +4957,9 @@
       </c>
     </row>
     <row r="132" spans="1:3">
-      <c r="A132" s="8"/>
+      <c r="A132" s="8">
+        <v>131</v>
+      </c>
       <c r="B132" s="7" t="s">
         <v>199</v>
       </c>
@@ -4816,7 +4968,9 @@
       </c>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="8"/>
+      <c r="A133" s="8">
+        <v>132</v>
+      </c>
       <c r="B133" s="7" t="s">
         <v>200</v>
       </c>
@@ -4825,7 +4979,9 @@
       </c>
     </row>
     <row r="134" spans="1:3">
-      <c r="A134" s="8"/>
+      <c r="A134" s="8">
+        <v>133</v>
+      </c>
       <c r="B134" s="7" t="s">
         <v>201</v>
       </c>
@@ -4834,7 +4990,9 @@
       </c>
     </row>
     <row r="135" spans="1:3">
-      <c r="A135" s="8"/>
+      <c r="A135" s="8">
+        <v>134</v>
+      </c>
       <c r="B135" s="7" t="s">
         <v>202</v>
       </c>
@@ -4843,7 +5001,9 @@
       </c>
     </row>
     <row r="136" spans="1:3">
-      <c r="A136" s="8"/>
+      <c r="A136" s="8">
+        <v>135</v>
+      </c>
       <c r="B136" s="7" t="s">
         <v>203</v>
       </c>
@@ -4852,7 +5012,9 @@
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="8"/>
+      <c r="A137" s="8">
+        <v>136</v>
+      </c>
       <c r="B137" s="7" t="s">
         <v>204</v>
       </c>
@@ -4861,7 +5023,9 @@
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="8"/>
+      <c r="A138" s="8">
+        <v>137</v>
+      </c>
       <c r="B138" s="7" t="s">
         <v>205</v>
       </c>
@@ -4870,7 +5034,9 @@
       </c>
     </row>
     <row r="139" spans="1:3">
-      <c r="A139" s="8"/>
+      <c r="A139" s="8">
+        <v>138</v>
+      </c>
       <c r="B139" s="7" t="s">
         <v>206</v>
       </c>
@@ -4879,7 +5045,9 @@
       </c>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="8"/>
+      <c r="A140" s="8">
+        <v>139</v>
+      </c>
       <c r="B140" s="7" t="s">
         <v>207</v>
       </c>
@@ -4888,7 +5056,9 @@
       </c>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141" s="8"/>
+      <c r="A141" s="8">
+        <v>140</v>
+      </c>
       <c r="B141" s="7" t="s">
         <v>208</v>
       </c>
@@ -4897,7 +5067,9 @@
       </c>
     </row>
     <row r="142" spans="1:3">
-      <c r="A142" s="8"/>
+      <c r="A142" s="8">
+        <v>141</v>
+      </c>
       <c r="B142" s="7" t="s">
         <v>209</v>
       </c>
@@ -4906,7 +5078,9 @@
       </c>
     </row>
     <row r="143" spans="1:3">
-      <c r="A143" s="8"/>
+      <c r="A143" s="8">
+        <v>142</v>
+      </c>
       <c r="B143" s="7" t="s">
         <v>210</v>
       </c>
@@ -4915,7 +5089,9 @@
       </c>
     </row>
     <row r="144" spans="1:3">
-      <c r="A144" s="8"/>
+      <c r="A144" s="8">
+        <v>143</v>
+      </c>
       <c r="B144" s="7" t="s">
         <v>211</v>
       </c>
@@ -4924,7 +5100,9 @@
       </c>
     </row>
     <row r="145" spans="1:3">
-      <c r="A145" s="8"/>
+      <c r="A145" s="8">
+        <v>144</v>
+      </c>
       <c r="B145" s="7" t="s">
         <v>212</v>
       </c>
@@ -4933,7 +5111,9 @@
       </c>
     </row>
     <row r="146" spans="1:3">
-      <c r="A146" s="8"/>
+      <c r="A146" s="8">
+        <v>145</v>
+      </c>
       <c r="B146" s="7" t="s">
         <v>213</v>
       </c>
@@ -4942,7 +5122,9 @@
       </c>
     </row>
     <row r="147" spans="1:3">
-      <c r="A147" s="8"/>
+      <c r="A147" s="8">
+        <v>146</v>
+      </c>
       <c r="B147" s="7" t="s">
         <v>214</v>
       </c>
@@ -4951,7 +5133,9 @@
       </c>
     </row>
     <row r="148" spans="1:3">
-      <c r="A148" s="8"/>
+      <c r="A148" s="8">
+        <v>147</v>
+      </c>
       <c r="B148" s="7" t="s">
         <v>215</v>
       </c>
@@ -4960,7 +5144,9 @@
       </c>
     </row>
     <row r="149" spans="1:3">
-      <c r="A149" s="8"/>
+      <c r="A149" s="8">
+        <v>148</v>
+      </c>
       <c r="B149" s="7" t="s">
         <v>216</v>
       </c>
@@ -4969,7 +5155,9 @@
       </c>
     </row>
     <row r="150" spans="1:3">
-      <c r="A150" s="8"/>
+      <c r="A150" s="8">
+        <v>149</v>
+      </c>
       <c r="B150" s="7" t="s">
         <v>217</v>
       </c>
@@ -4978,7 +5166,9 @@
       </c>
     </row>
     <row r="151" spans="1:3">
-      <c r="A151" s="8"/>
+      <c r="A151" s="8">
+        <v>150</v>
+      </c>
       <c r="B151" s="7" t="s">
         <v>218</v>
       </c>
@@ -4987,7 +5177,9 @@
       </c>
     </row>
     <row r="152" spans="1:3">
-      <c r="A152" s="8"/>
+      <c r="A152" s="8">
+        <v>151</v>
+      </c>
       <c r="B152" s="7" t="s">
         <v>219</v>
       </c>
@@ -4996,7 +5188,9 @@
       </c>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153" s="8"/>
+      <c r="A153" s="8">
+        <v>152</v>
+      </c>
       <c r="B153" s="7" t="s">
         <v>220</v>
       </c>
@@ -5005,7 +5199,9 @@
       </c>
     </row>
     <row r="154" spans="1:3">
-      <c r="A154" s="8"/>
+      <c r="A154" s="8">
+        <v>153</v>
+      </c>
       <c r="B154" s="7" t="s">
         <v>221</v>
       </c>
@@ -5014,7 +5210,9 @@
       </c>
     </row>
     <row r="155" spans="1:3">
-      <c r="A155" s="8"/>
+      <c r="A155" s="8">
+        <v>154</v>
+      </c>
       <c r="B155" s="7" t="s">
         <v>222</v>
       </c>
@@ -5023,7 +5221,9 @@
       </c>
     </row>
     <row r="156" spans="1:3">
-      <c r="A156" s="8"/>
+      <c r="A156" s="8">
+        <v>155</v>
+      </c>
       <c r="B156" s="7" t="s">
         <v>223</v>
       </c>
@@ -5032,7 +5232,9 @@
       </c>
     </row>
     <row r="157" spans="1:3">
-      <c r="A157" s="8"/>
+      <c r="A157" s="8">
+        <v>156</v>
+      </c>
       <c r="B157" s="7" t="s">
         <v>224</v>
       </c>
@@ -5041,7 +5243,9 @@
       </c>
     </row>
     <row r="158" spans="1:3">
-      <c r="A158" s="8"/>
+      <c r="A158" s="8">
+        <v>157</v>
+      </c>
       <c r="B158" s="7" t="s">
         <v>225</v>
       </c>
@@ -5050,7 +5254,9 @@
       </c>
     </row>
     <row r="159" spans="1:3">
-      <c r="A159" s="8"/>
+      <c r="A159" s="8">
+        <v>158</v>
+      </c>
       <c r="B159" s="7" t="s">
         <v>226</v>
       </c>
@@ -5059,7 +5265,9 @@
       </c>
     </row>
     <row r="160" spans="1:3">
-      <c r="A160" s="8"/>
+      <c r="A160" s="8">
+        <v>159</v>
+      </c>
       <c r="B160" s="7" t="s">
         <v>227</v>
       </c>
@@ -5068,7 +5276,9 @@
       </c>
     </row>
     <row r="161" spans="1:3">
-      <c r="A161" s="8"/>
+      <c r="A161" s="8">
+        <v>160</v>
+      </c>
       <c r="B161" s="7" t="s">
         <v>228</v>
       </c>
@@ -5077,7 +5287,9 @@
       </c>
     </row>
     <row r="162" spans="1:3">
-      <c r="A162" s="8"/>
+      <c r="A162" s="8">
+        <v>161</v>
+      </c>
       <c r="B162" s="7" t="s">
         <v>229</v>
       </c>
@@ -5086,7 +5298,9 @@
       </c>
     </row>
     <row r="163" spans="1:3">
-      <c r="A163" s="8"/>
+      <c r="A163" s="8">
+        <v>162</v>
+      </c>
       <c r="B163" s="7" t="s">
         <v>230</v>
       </c>
@@ -5095,7 +5309,9 @@
       </c>
     </row>
     <row r="164" spans="1:3">
-      <c r="A164" s="8"/>
+      <c r="A164" s="8">
+        <v>163</v>
+      </c>
       <c r="B164" s="7" t="s">
         <v>231</v>
       </c>
@@ -5104,7 +5320,9 @@
       </c>
     </row>
     <row r="165" spans="1:3">
-      <c r="A165" s="8"/>
+      <c r="A165" s="8">
+        <v>164</v>
+      </c>
       <c r="B165" s="7" t="s">
         <v>232</v>
       </c>
@@ -5113,7 +5331,9 @@
       </c>
     </row>
     <row r="166" spans="1:3">
-      <c r="A166" s="8"/>
+      <c r="A166" s="8">
+        <v>165</v>
+      </c>
       <c r="B166" s="7" t="s">
         <v>233</v>
       </c>
@@ -5122,7 +5342,9 @@
       </c>
     </row>
     <row r="167" spans="1:3">
-      <c r="A167" s="8"/>
+      <c r="A167" s="8">
+        <v>166</v>
+      </c>
       <c r="B167" s="7" t="s">
         <v>234</v>
       </c>
@@ -5131,7 +5353,9 @@
       </c>
     </row>
     <row r="168" spans="1:3">
-      <c r="A168" s="8"/>
+      <c r="A168" s="8">
+        <v>167</v>
+      </c>
       <c r="B168" s="7" t="s">
         <v>235</v>
       </c>
@@ -5140,7 +5364,9 @@
       </c>
     </row>
     <row r="169" spans="1:3">
-      <c r="A169" s="8"/>
+      <c r="A169" s="8">
+        <v>168</v>
+      </c>
       <c r="B169" s="7" t="s">
         <v>236</v>
       </c>
@@ -5149,7 +5375,9 @@
       </c>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170" s="8"/>
+      <c r="A170" s="8">
+        <v>169</v>
+      </c>
       <c r="B170" s="7" t="s">
         <v>237</v>
       </c>
@@ -5158,7 +5386,9 @@
       </c>
     </row>
     <row r="171" spans="1:3">
-      <c r="A171" s="8"/>
+      <c r="A171" s="8">
+        <v>170</v>
+      </c>
       <c r="B171" s="7" t="s">
         <v>238</v>
       </c>
@@ -5167,7 +5397,9 @@
       </c>
     </row>
     <row r="172" spans="1:3">
-      <c r="A172" s="8"/>
+      <c r="A172" s="8">
+        <v>171</v>
+      </c>
       <c r="B172" s="7" t="s">
         <v>239</v>
       </c>
@@ -5176,7 +5408,9 @@
       </c>
     </row>
     <row r="173" spans="1:3">
-      <c r="A173" s="8"/>
+      <c r="A173" s="8">
+        <v>172</v>
+      </c>
       <c r="B173" s="7" t="s">
         <v>240</v>
       </c>
@@ -5185,7 +5419,9 @@
       </c>
     </row>
     <row r="174" spans="1:3">
-      <c r="A174" s="8"/>
+      <c r="A174" s="8">
+        <v>173</v>
+      </c>
       <c r="B174" s="7" t="s">
         <v>241</v>
       </c>
@@ -5194,7 +5430,9 @@
       </c>
     </row>
     <row r="175" spans="1:3">
-      <c r="A175" s="8"/>
+      <c r="A175" s="8">
+        <v>174</v>
+      </c>
       <c r="B175" s="7" t="s">
         <v>242</v>
       </c>
@@ -5203,7 +5441,9 @@
       </c>
     </row>
     <row r="176" spans="1:3">
-      <c r="A176" s="8"/>
+      <c r="A176" s="8">
+        <v>175</v>
+      </c>
       <c r="B176" s="7" t="s">
         <v>243</v>
       </c>
@@ -5212,7 +5452,9 @@
       </c>
     </row>
     <row r="177" spans="1:3">
-      <c r="A177" s="8"/>
+      <c r="A177" s="8">
+        <v>176</v>
+      </c>
       <c r="B177" s="7" t="s">
         <v>244</v>
       </c>
@@ -5221,7 +5463,9 @@
       </c>
     </row>
     <row r="178" spans="1:3">
-      <c r="A178" s="8"/>
+      <c r="A178" s="8">
+        <v>177</v>
+      </c>
       <c r="B178" s="7" t="s">
         <v>245</v>
       </c>
@@ -5230,7 +5474,9 @@
       </c>
     </row>
     <row r="179" spans="1:3">
-      <c r="A179" s="8"/>
+      <c r="A179" s="8">
+        <v>178</v>
+      </c>
       <c r="B179" s="7" t="s">
         <v>246</v>
       </c>
@@ -5239,7 +5485,9 @@
       </c>
     </row>
     <row r="180" spans="1:3">
-      <c r="A180" s="8"/>
+      <c r="A180" s="8">
+        <v>179</v>
+      </c>
       <c r="B180" s="7" t="s">
         <v>247</v>
       </c>
@@ -5248,7 +5496,9 @@
       </c>
     </row>
     <row r="181" spans="1:3">
-      <c r="A181" s="8"/>
+      <c r="A181" s="8">
+        <v>180</v>
+      </c>
       <c r="B181" s="7" t="s">
         <v>248</v>
       </c>
@@ -5257,7 +5507,9 @@
       </c>
     </row>
     <row r="182" spans="1:3">
-      <c r="A182" s="8"/>
+      <c r="A182" s="8">
+        <v>181</v>
+      </c>
       <c r="B182" s="7" t="s">
         <v>249</v>
       </c>
@@ -5266,7 +5518,9 @@
       </c>
     </row>
     <row r="183" spans="1:3">
-      <c r="A183" s="8"/>
+      <c r="A183" s="8">
+        <v>182</v>
+      </c>
       <c r="B183" s="7" t="s">
         <v>250</v>
       </c>
@@ -5275,7 +5529,9 @@
       </c>
     </row>
     <row r="184" spans="1:3">
-      <c r="A184" s="8"/>
+      <c r="A184" s="8">
+        <v>183</v>
+      </c>
       <c r="B184" s="7" t="s">
         <v>251</v>
       </c>
@@ -5284,7 +5540,9 @@
       </c>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185" s="8"/>
+      <c r="A185" s="8">
+        <v>184</v>
+      </c>
       <c r="B185" s="7" t="s">
         <v>252</v>
       </c>
@@ -5293,7 +5551,9 @@
       </c>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="8"/>
+      <c r="A186" s="8">
+        <v>185</v>
+      </c>
       <c r="B186" s="7" t="s">
         <v>253</v>
       </c>
@@ -5302,7 +5562,9 @@
       </c>
     </row>
     <row r="187" spans="1:3">
-      <c r="A187" s="8"/>
+      <c r="A187" s="8">
+        <v>186</v>
+      </c>
       <c r="B187" s="7" t="s">
         <v>254</v>
       </c>
@@ -5311,7 +5573,9 @@
       </c>
     </row>
     <row r="188" spans="1:3">
-      <c r="A188" s="8"/>
+      <c r="A188" s="8">
+        <v>187</v>
+      </c>
       <c r="B188" s="7" t="s">
         <v>255</v>
       </c>
@@ -5320,7 +5584,9 @@
       </c>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189" s="8"/>
+      <c r="A189" s="8">
+        <v>188</v>
+      </c>
       <c r="B189" s="7" t="s">
         <v>256</v>
       </c>
@@ -5329,7 +5595,9 @@
       </c>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190" s="8"/>
+      <c r="A190" s="8">
+        <v>189</v>
+      </c>
       <c r="B190" s="7" t="s">
         <v>257</v>
       </c>
@@ -5338,7 +5606,9 @@
       </c>
     </row>
     <row r="191" spans="1:3">
-      <c r="A191" s="8"/>
+      <c r="A191" s="8">
+        <v>190</v>
+      </c>
       <c r="B191" s="7" t="s">
         <v>258</v>
       </c>
@@ -5347,7 +5617,9 @@
       </c>
     </row>
     <row r="192" spans="1:3">
-      <c r="A192" s="8"/>
+      <c r="A192" s="8">
+        <v>191</v>
+      </c>
       <c r="B192" s="7" t="s">
         <v>259</v>
       </c>
@@ -5356,7 +5628,9 @@
       </c>
     </row>
     <row r="193" spans="1:3">
-      <c r="A193" s="8"/>
+      <c r="A193" s="8">
+        <v>192</v>
+      </c>
       <c r="B193" s="7" t="s">
         <v>260</v>
       </c>
@@ -5365,7 +5639,9 @@
       </c>
     </row>
     <row r="194" spans="1:3">
-      <c r="A194" s="8"/>
+      <c r="A194" s="8">
+        <v>193</v>
+      </c>
       <c r="B194" s="7" t="s">
         <v>261</v>
       </c>
@@ -5374,7 +5650,9 @@
       </c>
     </row>
     <row r="195" spans="1:3">
-      <c r="A195" s="8"/>
+      <c r="A195" s="8">
+        <v>194</v>
+      </c>
       <c r="B195" s="7" t="s">
         <v>262</v>
       </c>
@@ -5383,7 +5661,9 @@
       </c>
     </row>
     <row r="196" spans="1:3">
-      <c r="A196" s="8"/>
+      <c r="A196" s="8">
+        <v>195</v>
+      </c>
       <c r="B196" s="7" t="s">
         <v>263</v>
       </c>
@@ -5392,7 +5672,9 @@
       </c>
     </row>
     <row r="197" spans="1:3">
-      <c r="A197" s="8"/>
+      <c r="A197" s="8">
+        <v>196</v>
+      </c>
       <c r="B197" s="7" t="s">
         <v>264</v>
       </c>
@@ -5401,7 +5683,9 @@
       </c>
     </row>
     <row r="198" spans="1:3">
-      <c r="A198" s="8"/>
+      <c r="A198" s="8">
+        <v>197</v>
+      </c>
       <c r="B198" s="7" t="s">
         <v>265</v>
       </c>
@@ -5410,7 +5694,9 @@
       </c>
     </row>
     <row r="199" spans="1:3">
-      <c r="A199" s="8"/>
+      <c r="A199" s="8">
+        <v>198</v>
+      </c>
       <c r="B199" s="7" t="s">
         <v>266</v>
       </c>
@@ -5419,7 +5705,9 @@
       </c>
     </row>
     <row r="200" spans="1:3">
-      <c r="A200" s="8"/>
+      <c r="A200" s="8">
+        <v>199</v>
+      </c>
       <c r="B200" s="7" t="s">
         <v>267</v>
       </c>
@@ -5428,7 +5716,9 @@
       </c>
     </row>
     <row r="201" spans="1:3">
-      <c r="A201" s="8"/>
+      <c r="A201" s="8">
+        <v>200</v>
+      </c>
       <c r="B201" s="7" t="s">
         <v>268</v>
       </c>
@@ -5437,7 +5727,9 @@
       </c>
     </row>
     <row r="202" spans="1:3">
-      <c r="A202" s="8"/>
+      <c r="A202" s="8">
+        <v>201</v>
+      </c>
       <c r="B202" s="7" t="s">
         <v>269</v>
       </c>
@@ -5446,7 +5738,9 @@
       </c>
     </row>
     <row r="203" spans="1:3">
-      <c r="A203" s="8"/>
+      <c r="A203" s="8">
+        <v>202</v>
+      </c>
       <c r="B203" s="7" t="s">
         <v>270</v>
       </c>
@@ -5455,7 +5749,9 @@
       </c>
     </row>
     <row r="204" spans="1:3">
-      <c r="A204" s="8"/>
+      <c r="A204" s="8">
+        <v>203</v>
+      </c>
       <c r="B204" s="7" t="s">
         <v>271</v>
       </c>
@@ -5464,7 +5760,9 @@
       </c>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205" s="8"/>
+      <c r="A205" s="8">
+        <v>204</v>
+      </c>
       <c r="B205" s="7" t="s">
         <v>272</v>
       </c>
@@ -5473,7 +5771,9 @@
       </c>
     </row>
     <row r="206" spans="1:3">
-      <c r="A206" s="8"/>
+      <c r="A206" s="8">
+        <v>205</v>
+      </c>
       <c r="B206" s="7" t="s">
         <v>273</v>
       </c>
@@ -5482,7 +5782,9 @@
       </c>
     </row>
     <row r="207" spans="1:3">
-      <c r="A207" s="8"/>
+      <c r="A207" s="8">
+        <v>206</v>
+      </c>
       <c r="B207" s="7" t="s">
         <v>274</v>
       </c>
@@ -5491,7 +5793,9 @@
       </c>
     </row>
     <row r="208" spans="1:3">
-      <c r="A208" s="8"/>
+      <c r="A208" s="8">
+        <v>207</v>
+      </c>
       <c r="B208" s="7" t="s">
         <v>275</v>
       </c>
@@ -5500,7 +5804,9 @@
       </c>
     </row>
     <row r="209" spans="1:3">
-      <c r="A209" s="8"/>
+      <c r="A209" s="8">
+        <v>208</v>
+      </c>
       <c r="B209" s="7" t="s">
         <v>276</v>
       </c>
@@ -5509,7 +5815,9 @@
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="8"/>
+      <c r="A210" s="8">
+        <v>209</v>
+      </c>
       <c r="B210" s="7" t="s">
         <v>277</v>
       </c>
@@ -5518,7 +5826,9 @@
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="8"/>
+      <c r="A211" s="8">
+        <v>210</v>
+      </c>
       <c r="B211" s="7" t="s">
         <v>278</v>
       </c>
@@ -5527,7 +5837,9 @@
       </c>
     </row>
     <row r="212" spans="1:3">
-      <c r="A212" s="8"/>
+      <c r="A212" s="8">
+        <v>211</v>
+      </c>
       <c r="B212" s="7" t="s">
         <v>279</v>
       </c>
@@ -5536,7 +5848,9 @@
       </c>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="8"/>
+      <c r="A213" s="8">
+        <v>212</v>
+      </c>
       <c r="B213" s="7" t="s">
         <v>280</v>
       </c>
@@ -5545,7 +5859,9 @@
       </c>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="8"/>
+      <c r="A214" s="8">
+        <v>213</v>
+      </c>
       <c r="B214" s="7" t="s">
         <v>281</v>
       </c>
@@ -5554,7 +5870,9 @@
       </c>
     </row>
     <row r="215" spans="1:3">
-      <c r="A215" s="8"/>
+      <c r="A215" s="8">
+        <v>214</v>
+      </c>
       <c r="B215" s="7" t="s">
         <v>282</v>
       </c>
@@ -5563,7 +5881,9 @@
       </c>
     </row>
     <row r="216" spans="1:3">
-      <c r="A216" s="8"/>
+      <c r="A216" s="8">
+        <v>215</v>
+      </c>
       <c r="B216" s="7" t="s">
         <v>283</v>
       </c>
@@ -5572,7 +5892,9 @@
       </c>
     </row>
     <row r="217" spans="1:3">
-      <c r="A217" s="8"/>
+      <c r="A217" s="8">
+        <v>216</v>
+      </c>
       <c r="B217" s="7" t="s">
         <v>284</v>
       </c>
@@ -5581,7 +5903,9 @@
       </c>
     </row>
     <row r="218" spans="1:3">
-      <c r="A218" s="8"/>
+      <c r="A218" s="8">
+        <v>217</v>
+      </c>
       <c r="B218" s="7" t="s">
         <v>285</v>
       </c>
@@ -5590,7 +5914,9 @@
       </c>
     </row>
     <row r="219" spans="1:3">
-      <c r="A219" s="8"/>
+      <c r="A219" s="8">
+        <v>218</v>
+      </c>
       <c r="B219" s="7" t="s">
         <v>286</v>
       </c>
@@ -5599,7 +5925,9 @@
       </c>
     </row>
     <row r="220" spans="1:3">
-      <c r="A220" s="8"/>
+      <c r="A220" s="8">
+        <v>219</v>
+      </c>
       <c r="B220" s="7" t="s">
         <v>287</v>
       </c>
@@ -5608,7 +5936,9 @@
       </c>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221" s="8"/>
+      <c r="A221" s="8">
+        <v>220</v>
+      </c>
       <c r="B221" s="7" t="s">
         <v>288</v>
       </c>
@@ -5617,7 +5947,9 @@
       </c>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="8"/>
+      <c r="A222" s="8">
+        <v>221</v>
+      </c>
       <c r="B222" s="7" t="s">
         <v>289</v>
       </c>
@@ -5626,7 +5958,9 @@
       </c>
     </row>
     <row r="223" spans="1:3">
-      <c r="A223" s="8"/>
+      <c r="A223" s="8">
+        <v>222</v>
+      </c>
       <c r="B223" s="7" t="s">
         <v>290</v>
       </c>
@@ -5635,7 +5969,9 @@
       </c>
     </row>
     <row r="224" spans="1:3">
-      <c r="A224" s="8"/>
+      <c r="A224" s="8">
+        <v>223</v>
+      </c>
       <c r="B224" s="7" t="s">
         <v>291</v>
       </c>
@@ -5644,7 +5980,9 @@
       </c>
     </row>
     <row r="225" spans="1:3">
-      <c r="A225" s="8"/>
+      <c r="A225" s="8">
+        <v>224</v>
+      </c>
       <c r="B225" s="7" t="s">
         <v>292</v>
       </c>
@@ -5653,7 +5991,9 @@
       </c>
     </row>
     <row r="226" spans="1:3">
-      <c r="A226" s="8"/>
+      <c r="A226" s="8">
+        <v>225</v>
+      </c>
       <c r="B226" s="7" t="s">
         <v>293</v>
       </c>
@@ -5662,7 +6002,9 @@
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="8"/>
+      <c r="A227" s="8">
+        <v>226</v>
+      </c>
       <c r="B227" s="7" t="s">
         <v>294</v>
       </c>
@@ -5671,7 +6013,9 @@
       </c>
     </row>
     <row r="228" spans="1:3">
-      <c r="A228" s="8"/>
+      <c r="A228" s="8">
+        <v>227</v>
+      </c>
       <c r="B228" s="7" t="s">
         <v>295</v>
       </c>
@@ -5680,7 +6024,9 @@
       </c>
     </row>
     <row r="229" spans="1:3">
-      <c r="A229" s="8"/>
+      <c r="A229" s="8">
+        <v>228</v>
+      </c>
       <c r="B229" s="7" t="s">
         <v>296</v>
       </c>
@@ -5689,7 +6035,9 @@
       </c>
     </row>
     <row r="230" spans="1:3">
-      <c r="A230" s="8"/>
+      <c r="A230" s="8">
+        <v>229</v>
+      </c>
       <c r="B230" s="7" t="s">
         <v>297</v>
       </c>
@@ -5698,7 +6046,9 @@
       </c>
     </row>
     <row r="231" spans="1:3">
-      <c r="A231" s="8"/>
+      <c r="A231" s="8">
+        <v>230</v>
+      </c>
       <c r="B231" s="7" t="s">
         <v>298</v>
       </c>
@@ -5707,7 +6057,9 @@
       </c>
     </row>
     <row r="232" spans="1:3">
-      <c r="A232" s="8"/>
+      <c r="A232" s="8">
+        <v>231</v>
+      </c>
       <c r="B232" s="7" t="s">
         <v>299</v>
       </c>
@@ -5716,7 +6068,9 @@
       </c>
     </row>
     <row r="233" spans="1:3">
-      <c r="A233" s="8"/>
+      <c r="A233" s="8">
+        <v>232</v>
+      </c>
       <c r="B233" s="7" t="s">
         <v>300</v>
       </c>
@@ -5725,7 +6079,9 @@
       </c>
     </row>
     <row r="234" spans="1:3">
-      <c r="A234" s="8"/>
+      <c r="A234" s="8">
+        <v>233</v>
+      </c>
       <c r="B234" s="7" t="s">
         <v>301</v>
       </c>
@@ -5734,7 +6090,9 @@
       </c>
     </row>
     <row r="235" spans="1:3">
-      <c r="A235" s="8"/>
+      <c r="A235" s="8">
+        <v>234</v>
+      </c>
       <c r="B235" s="7" t="s">
         <v>302</v>
       </c>
@@ -5743,7 +6101,9 @@
       </c>
     </row>
     <row r="236" spans="1:3">
-      <c r="A236" s="8"/>
+      <c r="A236" s="8">
+        <v>235</v>
+      </c>
       <c r="B236" s="7" t="s">
         <v>303</v>
       </c>
@@ -5752,7 +6112,9 @@
       </c>
     </row>
     <row r="237" spans="1:3">
-      <c r="A237" s="8"/>
+      <c r="A237" s="8">
+        <v>236</v>
+      </c>
       <c r="B237" s="7" t="s">
         <v>304</v>
       </c>
@@ -5761,7 +6123,9 @@
       </c>
     </row>
     <row r="238" spans="1:3">
-      <c r="A238" s="8"/>
+      <c r="A238" s="8">
+        <v>237</v>
+      </c>
       <c r="B238" s="7" t="s">
         <v>305</v>
       </c>
@@ -5770,7 +6134,9 @@
       </c>
     </row>
     <row r="239" spans="1:3">
-      <c r="A239" s="8"/>
+      <c r="A239" s="8">
+        <v>238</v>
+      </c>
       <c r="B239" s="7" t="s">
         <v>306</v>
       </c>
@@ -5779,7 +6145,9 @@
       </c>
     </row>
     <row r="240" spans="1:3">
-      <c r="A240" s="8"/>
+      <c r="A240" s="8">
+        <v>239</v>
+      </c>
       <c r="B240" s="7" t="s">
         <v>307</v>
       </c>
@@ -5788,7 +6156,9 @@
       </c>
     </row>
     <row r="241" spans="1:3">
-      <c r="A241" s="8"/>
+      <c r="A241" s="8">
+        <v>240</v>
+      </c>
       <c r="B241" s="7" t="s">
         <v>308</v>
       </c>
@@ -5797,7 +6167,9 @@
       </c>
     </row>
     <row r="242" spans="1:3">
-      <c r="A242" s="8"/>
+      <c r="A242" s="8">
+        <v>241</v>
+      </c>
       <c r="B242" s="7" t="s">
         <v>309</v>
       </c>
@@ -5806,7 +6178,9 @@
       </c>
     </row>
     <row r="243" spans="1:3">
-      <c r="A243" s="8"/>
+      <c r="A243" s="8">
+        <v>242</v>
+      </c>
       <c r="B243" s="7" t="s">
         <v>310</v>
       </c>
@@ -5815,7 +6189,9 @@
       </c>
     </row>
     <row r="244" spans="1:3">
-      <c r="A244" s="8"/>
+      <c r="A244" s="8">
+        <v>243</v>
+      </c>
       <c r="B244" s="7" t="s">
         <v>311</v>
       </c>
@@ -5824,7 +6200,9 @@
       </c>
     </row>
     <row r="245" spans="1:3">
-      <c r="A245" s="8"/>
+      <c r="A245" s="8">
+        <v>244</v>
+      </c>
       <c r="B245" s="7" t="s">
         <v>312</v>
       </c>
@@ -5833,7 +6211,9 @@
       </c>
     </row>
     <row r="246" spans="1:3">
-      <c r="A246" s="8"/>
+      <c r="A246" s="8">
+        <v>245</v>
+      </c>
       <c r="B246" s="7" t="s">
         <v>313</v>
       </c>
@@ -5842,7 +6222,9 @@
       </c>
     </row>
     <row r="247" spans="1:3">
-      <c r="A247" s="8"/>
+      <c r="A247" s="8">
+        <v>246</v>
+      </c>
       <c r="B247" s="7" t="s">
         <v>314</v>
       </c>
@@ -5851,7 +6233,9 @@
       </c>
     </row>
     <row r="248" spans="1:3">
-      <c r="A248" s="8"/>
+      <c r="A248" s="8">
+        <v>247</v>
+      </c>
       <c r="B248" s="7" t="s">
         <v>315</v>
       </c>
@@ -5860,7 +6244,9 @@
       </c>
     </row>
     <row r="249" spans="1:3">
-      <c r="A249" s="8"/>
+      <c r="A249" s="8">
+        <v>248</v>
+      </c>
       <c r="B249" s="7" t="s">
         <v>316</v>
       </c>
@@ -5869,7 +6255,9 @@
       </c>
     </row>
     <row r="250" spans="1:3">
-      <c r="A250" s="8"/>
+      <c r="A250" s="8">
+        <v>249</v>
+      </c>
       <c r="B250" s="7" t="s">
         <v>317</v>
       </c>
@@ -5878,7 +6266,9 @@
       </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251" s="8"/>
+      <c r="A251" s="8">
+        <v>250</v>
+      </c>
       <c r="B251" s="7" t="s">
         <v>318</v>
       </c>
@@ -5887,7 +6277,9 @@
       </c>
     </row>
     <row r="252" spans="1:3">
-      <c r="A252" s="8"/>
+      <c r="A252" s="8">
+        <v>251</v>
+      </c>
       <c r="B252" s="7" t="s">
         <v>319</v>
       </c>
@@ -5896,7 +6288,9 @@
       </c>
     </row>
     <row r="253" spans="1:3">
-      <c r="A253" s="8"/>
+      <c r="A253" s="8">
+        <v>252</v>
+      </c>
       <c r="B253" s="7" t="s">
         <v>320</v>
       </c>
@@ -5905,7 +6299,9 @@
       </c>
     </row>
     <row r="254" spans="1:3">
-      <c r="A254" s="8"/>
+      <c r="A254" s="8">
+        <v>253</v>
+      </c>
       <c r="B254" s="7" t="s">
         <v>321</v>
       </c>
@@ -5914,7 +6310,9 @@
       </c>
     </row>
     <row r="255" spans="1:3">
-      <c r="A255" s="8"/>
+      <c r="A255" s="8">
+        <v>254</v>
+      </c>
       <c r="B255" s="7" t="s">
         <v>322</v>
       </c>
@@ -5923,7 +6321,9 @@
       </c>
     </row>
     <row r="256" spans="1:3">
-      <c r="A256" s="8"/>
+      <c r="A256" s="8">
+        <v>255</v>
+      </c>
       <c r="B256" s="7" t="s">
         <v>323</v>
       </c>
@@ -5932,7 +6332,9 @@
       </c>
     </row>
     <row r="257" spans="1:3">
-      <c r="A257" s="8"/>
+      <c r="A257" s="8">
+        <v>256</v>
+      </c>
       <c r="B257" s="7" t="s">
         <v>324</v>
       </c>
@@ -5941,7 +6343,9 @@
       </c>
     </row>
     <row r="258" spans="1:3">
-      <c r="A258" s="8"/>
+      <c r="A258" s="8">
+        <v>257</v>
+      </c>
       <c r="B258" s="7" t="s">
         <v>325</v>
       </c>
@@ -5950,7 +6354,9 @@
       </c>
     </row>
     <row r="259" spans="1:3">
-      <c r="A259" s="8"/>
+      <c r="A259" s="8">
+        <v>258</v>
+      </c>
       <c r="B259" s="7" t="s">
         <v>326</v>
       </c>
@@ -5959,7 +6365,9 @@
       </c>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260" s="8"/>
+      <c r="A260" s="8">
+        <v>259</v>
+      </c>
       <c r="B260" s="7" t="s">
         <v>327</v>
       </c>
@@ -5968,7 +6376,9 @@
       </c>
     </row>
     <row r="261" spans="1:3">
-      <c r="A261" s="8"/>
+      <c r="A261" s="8">
+        <v>260</v>
+      </c>
       <c r="B261" s="7" t="s">
         <v>328</v>
       </c>
@@ -5977,7 +6387,9 @@
       </c>
     </row>
     <row r="262" spans="1:3">
-      <c r="A262" s="8"/>
+      <c r="A262" s="8">
+        <v>261</v>
+      </c>
       <c r="B262" s="7" t="s">
         <v>329</v>
       </c>
@@ -5986,7 +6398,9 @@
       </c>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="8"/>
+      <c r="A263" s="8">
+        <v>262</v>
+      </c>
       <c r="B263" s="7" t="s">
         <v>330</v>
       </c>
@@ -5995,7 +6409,9 @@
       </c>
     </row>
     <row r="264" spans="1:3">
-      <c r="A264" s="8"/>
+      <c r="A264" s="8">
+        <v>263</v>
+      </c>
       <c r="B264" s="7" t="s">
         <v>331</v>
       </c>
@@ -6004,7 +6420,9 @@
       </c>
     </row>
     <row r="265" spans="1:3">
-      <c r="A265" s="8"/>
+      <c r="A265" s="8">
+        <v>264</v>
+      </c>
       <c r="B265" s="7" t="s">
         <v>332</v>
       </c>
@@ -6013,7 +6431,9 @@
       </c>
     </row>
     <row r="266" spans="1:3">
-      <c r="A266" s="8"/>
+      <c r="A266" s="8">
+        <v>265</v>
+      </c>
       <c r="B266" s="7" t="s">
         <v>333</v>
       </c>
@@ -6022,7 +6442,9 @@
       </c>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267" s="8"/>
+      <c r="A267" s="8">
+        <v>266</v>
+      </c>
       <c r="B267" s="7" t="s">
         <v>334</v>
       </c>
@@ -6031,7 +6453,9 @@
       </c>
     </row>
     <row r="268" spans="1:3">
-      <c r="A268" s="8"/>
+      <c r="A268" s="8">
+        <v>267</v>
+      </c>
       <c r="B268" s="7" t="s">
         <v>335</v>
       </c>
@@ -6040,7 +6464,9 @@
       </c>
     </row>
     <row r="269" spans="1:3">
-      <c r="A269" s="8"/>
+      <c r="A269" s="8">
+        <v>268</v>
+      </c>
       <c r="B269" s="7" t="s">
         <v>336</v>
       </c>
@@ -6049,7 +6475,9 @@
       </c>
     </row>
     <row r="270" spans="1:3">
-      <c r="A270" s="8"/>
+      <c r="A270" s="8">
+        <v>269</v>
+      </c>
       <c r="B270" s="7" t="s">
         <v>337</v>
       </c>
@@ -6058,7 +6486,9 @@
       </c>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271" s="8"/>
+      <c r="A271" s="8">
+        <v>270</v>
+      </c>
       <c r="B271" s="7" t="s">
         <v>338</v>
       </c>
@@ -6067,7 +6497,9 @@
       </c>
     </row>
     <row r="272" spans="1:3">
-      <c r="A272" s="8"/>
+      <c r="A272" s="8">
+        <v>271</v>
+      </c>
       <c r="B272" s="7" t="s">
         <v>339</v>
       </c>
@@ -6076,7 +6508,9 @@
       </c>
     </row>
     <row r="273" spans="1:3">
-      <c r="A273" s="8"/>
+      <c r="A273" s="8">
+        <v>272</v>
+      </c>
       <c r="B273" s="7" t="s">
         <v>340</v>
       </c>
@@ -6085,7 +6519,9 @@
       </c>
     </row>
     <row r="274" spans="1:3">
-      <c r="A274" s="8"/>
+      <c r="A274" s="8">
+        <v>273</v>
+      </c>
       <c r="B274" s="7" t="s">
         <v>341</v>
       </c>
@@ -6094,7 +6530,9 @@
       </c>
     </row>
     <row r="275" spans="1:3">
-      <c r="A275" s="8"/>
+      <c r="A275" s="8">
+        <v>274</v>
+      </c>
       <c r="B275" s="7" t="s">
         <v>342</v>
       </c>
@@ -6103,7 +6541,9 @@
       </c>
     </row>
     <row r="276" spans="1:3">
-      <c r="A276" s="8"/>
+      <c r="A276" s="8">
+        <v>275</v>
+      </c>
       <c r="B276" s="7" t="s">
         <v>343</v>
       </c>
@@ -6112,7 +6552,9 @@
       </c>
     </row>
     <row r="277" spans="1:3">
-      <c r="A277" s="8"/>
+      <c r="A277" s="8">
+        <v>276</v>
+      </c>
       <c r="B277" s="7" t="s">
         <v>344</v>
       </c>
@@ -6121,7 +6563,9 @@
       </c>
     </row>
     <row r="278" spans="1:3">
-      <c r="A278" s="8"/>
+      <c r="A278" s="8">
+        <v>277</v>
+      </c>
       <c r="B278" s="7" t="s">
         <v>345</v>
       </c>
@@ -6130,7 +6574,9 @@
       </c>
     </row>
     <row r="279" spans="1:3">
-      <c r="A279" s="8"/>
+      <c r="A279" s="8">
+        <v>278</v>
+      </c>
       <c r="B279" s="7" t="s">
         <v>346</v>
       </c>
@@ -6139,7 +6585,9 @@
       </c>
     </row>
     <row r="280" spans="1:3">
-      <c r="A280" s="8"/>
+      <c r="A280" s="8">
+        <v>279</v>
+      </c>
       <c r="B280" s="7" t="s">
         <v>347</v>
       </c>
@@ -6148,7 +6596,9 @@
       </c>
     </row>
     <row r="281" spans="1:3">
-      <c r="A281" s="8"/>
+      <c r="A281" s="8">
+        <v>280</v>
+      </c>
       <c r="B281" s="7" t="s">
         <v>348</v>
       </c>
@@ -6157,7 +6607,9 @@
       </c>
     </row>
     <row r="282" spans="1:3">
-      <c r="A282" s="8"/>
+      <c r="A282" s="8">
+        <v>281</v>
+      </c>
       <c r="B282" s="7" t="s">
         <v>349</v>
       </c>
@@ -6166,7 +6618,9 @@
       </c>
     </row>
     <row r="283" spans="1:3">
-      <c r="A283" s="8"/>
+      <c r="A283" s="8">
+        <v>282</v>
+      </c>
       <c r="B283" s="7" t="s">
         <v>350</v>
       </c>
@@ -6175,7 +6629,9 @@
       </c>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284" s="8"/>
+      <c r="A284" s="8">
+        <v>283</v>
+      </c>
       <c r="B284" s="7" t="s">
         <v>351</v>
       </c>
@@ -6184,7 +6640,9 @@
       </c>
     </row>
     <row r="285" spans="1:3">
-      <c r="A285" s="8"/>
+      <c r="A285" s="8">
+        <v>284</v>
+      </c>
       <c r="B285" s="7" t="s">
         <v>352</v>
       </c>
@@ -6193,7 +6651,9 @@
       </c>
     </row>
     <row r="286" spans="1:3">
-      <c r="A286" s="8"/>
+      <c r="A286" s="8">
+        <v>285</v>
+      </c>
       <c r="B286" s="7" t="s">
         <v>353</v>
       </c>
@@ -6202,7 +6662,9 @@
       </c>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287" s="8"/>
+      <c r="A287" s="8">
+        <v>286</v>
+      </c>
       <c r="B287" s="7" t="s">
         <v>354</v>
       </c>
@@ -6211,7 +6673,9 @@
       </c>
     </row>
     <row r="288" spans="1:3">
-      <c r="A288" s="8"/>
+      <c r="A288" s="8">
+        <v>287</v>
+      </c>
       <c r="B288" s="7" t="s">
         <v>355</v>
       </c>
@@ -6220,7 +6684,9 @@
       </c>
     </row>
     <row r="289" spans="1:3">
-      <c r="A289" s="8"/>
+      <c r="A289" s="8">
+        <v>288</v>
+      </c>
       <c r="B289" s="7" t="s">
         <v>356</v>
       </c>
@@ -6229,7 +6695,9 @@
       </c>
     </row>
     <row r="290" spans="1:3">
-      <c r="A290" s="8"/>
+      <c r="A290" s="8">
+        <v>289</v>
+      </c>
       <c r="B290" s="7" t="s">
         <v>357</v>
       </c>
@@ -6238,7 +6706,9 @@
       </c>
     </row>
     <row r="291" spans="1:3">
-      <c r="A291" s="8"/>
+      <c r="A291" s="8">
+        <v>290</v>
+      </c>
       <c r="B291" s="7" t="s">
         <v>358</v>
       </c>
@@ -6247,7 +6717,9 @@
       </c>
     </row>
     <row r="292" spans="1:3">
-      <c r="A292" s="8"/>
+      <c r="A292" s="8">
+        <v>291</v>
+      </c>
       <c r="B292" s="7" t="s">
         <v>359</v>
       </c>
@@ -6256,7 +6728,9 @@
       </c>
     </row>
     <row r="293" spans="1:3">
-      <c r="A293" s="8"/>
+      <c r="A293" s="8">
+        <v>292</v>
+      </c>
       <c r="B293" s="7" t="s">
         <v>360</v>
       </c>
@@ -6265,7 +6739,9 @@
       </c>
     </row>
     <row r="294" spans="1:3">
-      <c r="A294" s="8"/>
+      <c r="A294" s="8">
+        <v>293</v>
+      </c>
       <c r="B294" s="7" t="s">
         <v>361</v>
       </c>
@@ -6274,7 +6750,9 @@
       </c>
     </row>
     <row r="295" spans="1:3">
-      <c r="A295" s="8"/>
+      <c r="A295" s="8">
+        <v>294</v>
+      </c>
       <c r="B295" s="7" t="s">
         <v>362</v>
       </c>
@@ -6283,7 +6761,9 @@
       </c>
     </row>
     <row r="296" spans="1:3">
-      <c r="A296" s="8"/>
+      <c r="A296" s="8">
+        <v>295</v>
+      </c>
       <c r="B296" s="7" t="s">
         <v>363</v>
       </c>
@@ -6292,7 +6772,9 @@
       </c>
     </row>
     <row r="297" spans="1:3">
-      <c r="A297" s="8"/>
+      <c r="A297" s="8">
+        <v>296</v>
+      </c>
       <c r="B297" s="7" t="s">
         <v>364</v>
       </c>
@@ -6301,7 +6783,9 @@
       </c>
     </row>
     <row r="298" spans="1:3">
-      <c r="A298" s="8"/>
+      <c r="A298" s="8">
+        <v>297</v>
+      </c>
       <c r="B298" s="7" t="s">
         <v>365</v>
       </c>
@@ -6310,7 +6794,9 @@
       </c>
     </row>
     <row r="299" spans="1:3">
-      <c r="A299" s="8"/>
+      <c r="A299" s="8">
+        <v>298</v>
+      </c>
       <c r="B299" s="7" t="s">
         <v>366</v>
       </c>
@@ -6319,7 +6805,9 @@
       </c>
     </row>
     <row r="300" spans="1:3">
-      <c r="A300" s="8"/>
+      <c r="A300" s="8">
+        <v>299</v>
+      </c>
       <c r="B300" s="7" t="s">
         <v>367</v>
       </c>
@@ -6328,7 +6816,9 @@
       </c>
     </row>
     <row r="301" spans="1:3">
-      <c r="A301" s="8"/>
+      <c r="A301" s="8">
+        <v>300</v>
+      </c>
       <c r="B301" s="7" t="s">
         <v>368</v>
       </c>
@@ -6337,7 +6827,9 @@
       </c>
     </row>
     <row r="302" spans="1:3">
-      <c r="A302" s="8"/>
+      <c r="A302" s="8">
+        <v>301</v>
+      </c>
       <c r="B302" s="7" t="s">
         <v>369</v>
       </c>
@@ -6346,7 +6838,9 @@
       </c>
     </row>
     <row r="303" spans="1:3">
-      <c r="A303" s="8"/>
+      <c r="A303" s="8">
+        <v>302</v>
+      </c>
       <c r="B303" s="7" t="s">
         <v>370</v>
       </c>
@@ -6355,7 +6849,9 @@
       </c>
     </row>
     <row r="304" spans="1:3">
-      <c r="A304" s="8"/>
+      <c r="A304" s="8">
+        <v>303</v>
+      </c>
       <c r="B304" s="7" t="s">
         <v>371</v>
       </c>
@@ -6364,7 +6860,9 @@
       </c>
     </row>
     <row r="305" spans="1:3">
-      <c r="A305" s="8"/>
+      <c r="A305" s="8">
+        <v>304</v>
+      </c>
       <c r="B305" s="7" t="s">
         <v>372</v>
       </c>
@@ -6373,7 +6871,9 @@
       </c>
     </row>
     <row r="306" spans="1:3">
-      <c r="A306" s="8"/>
+      <c r="A306" s="8">
+        <v>305</v>
+      </c>
       <c r="B306" s="7" t="s">
         <v>373</v>
       </c>
@@ -6382,7 +6882,9 @@
       </c>
     </row>
     <row r="307" spans="1:3">
-      <c r="A307" s="8"/>
+      <c r="A307" s="8">
+        <v>306</v>
+      </c>
       <c r="B307" s="7" t="s">
         <v>374</v>
       </c>
@@ -6391,7 +6893,9 @@
       </c>
     </row>
     <row r="308" spans="1:3">
-      <c r="A308" s="8"/>
+      <c r="A308" s="8">
+        <v>307</v>
+      </c>
       <c r="B308" s="7" t="s">
         <v>375</v>
       </c>
@@ -6400,7 +6904,9 @@
       </c>
     </row>
     <row r="309" spans="1:3">
-      <c r="A309" s="8"/>
+      <c r="A309" s="8">
+        <v>308</v>
+      </c>
       <c r="B309" s="7" t="s">
         <v>376</v>
       </c>
@@ -6409,7 +6915,9 @@
       </c>
     </row>
     <row r="310" spans="1:3">
-      <c r="A310" s="8"/>
+      <c r="A310" s="8">
+        <v>309</v>
+      </c>
       <c r="B310" s="7" t="s">
         <v>377</v>
       </c>
@@ -6418,7 +6926,9 @@
       </c>
     </row>
     <row r="311" spans="1:3">
-      <c r="A311" s="8"/>
+      <c r="A311" s="8">
+        <v>310</v>
+      </c>
       <c r="B311" s="7" t="s">
         <v>378</v>
       </c>
@@ -6427,7 +6937,9 @@
       </c>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="8"/>
+      <c r="A312" s="8">
+        <v>311</v>
+      </c>
       <c r="B312" s="7" t="s">
         <v>379</v>
       </c>
@@ -6436,7 +6948,9 @@
       </c>
     </row>
     <row r="313" spans="1:3">
-      <c r="A313" s="8"/>
+      <c r="A313" s="8">
+        <v>312</v>
+      </c>
       <c r="B313" s="7" t="s">
         <v>380</v>
       </c>
@@ -6445,7 +6959,9 @@
       </c>
     </row>
     <row r="314" spans="1:3">
-      <c r="A314" s="8"/>
+      <c r="A314" s="8">
+        <v>313</v>
+      </c>
       <c r="B314" s="7" t="s">
         <v>381</v>
       </c>
@@ -6454,7 +6970,9 @@
       </c>
     </row>
     <row r="315" spans="1:3">
-      <c r="A315" s="8"/>
+      <c r="A315" s="8">
+        <v>314</v>
+      </c>
       <c r="B315" s="7" t="s">
         <v>382</v>
       </c>
@@ -6463,7 +6981,9 @@
       </c>
     </row>
     <row r="316" spans="1:3">
-      <c r="A316" s="8"/>
+      <c r="A316" s="8">
+        <v>315</v>
+      </c>
       <c r="B316" s="7" t="s">
         <v>383</v>
       </c>
@@ -6472,7 +6992,9 @@
       </c>
     </row>
     <row r="317" spans="1:3">
-      <c r="A317" s="8"/>
+      <c r="A317" s="8">
+        <v>316</v>
+      </c>
       <c r="B317" s="7" t="s">
         <v>384</v>
       </c>
@@ -6481,7 +7003,9 @@
       </c>
     </row>
     <row r="318" spans="1:3">
-      <c r="A318" s="8"/>
+      <c r="A318" s="8">
+        <v>317</v>
+      </c>
       <c r="B318" s="7" t="s">
         <v>385</v>
       </c>
@@ -6490,7 +7014,9 @@
       </c>
     </row>
     <row r="319" spans="1:3">
-      <c r="A319" s="8"/>
+      <c r="A319" s="8">
+        <v>318</v>
+      </c>
       <c r="B319" s="7" t="s">
         <v>386</v>
       </c>
@@ -6499,7 +7025,9 @@
       </c>
     </row>
     <row r="320" spans="1:3">
-      <c r="A320" s="8"/>
+      <c r="A320" s="8">
+        <v>319</v>
+      </c>
       <c r="B320" s="7" t="s">
         <v>387</v>
       </c>
@@ -6508,7 +7036,9 @@
       </c>
     </row>
     <row r="321" spans="1:3">
-      <c r="A321" s="8"/>
+      <c r="A321" s="8">
+        <v>320</v>
+      </c>
       <c r="B321" s="7" t="s">
         <v>388</v>
       </c>
@@ -6517,7 +7047,9 @@
       </c>
     </row>
     <row r="322" spans="1:3">
-      <c r="A322" s="8"/>
+      <c r="A322" s="8">
+        <v>321</v>
+      </c>
       <c r="B322" s="7" t="s">
         <v>389</v>
       </c>
@@ -6526,7 +7058,9 @@
       </c>
     </row>
     <row r="323" spans="1:3">
-      <c r="A323" s="8"/>
+      <c r="A323" s="8">
+        <v>322</v>
+      </c>
       <c r="B323" s="7" t="s">
         <v>390</v>
       </c>
@@ -6535,7 +7069,9 @@
       </c>
     </row>
     <row r="324" spans="1:3">
-      <c r="A324" s="8"/>
+      <c r="A324" s="8">
+        <v>323</v>
+      </c>
       <c r="B324" s="7" t="s">
         <v>391</v>
       </c>
@@ -6544,7 +7080,9 @@
       </c>
     </row>
     <row r="325" spans="1:3">
-      <c r="A325" s="8"/>
+      <c r="A325" s="8">
+        <v>324</v>
+      </c>
       <c r="B325" s="7" t="s">
         <v>392</v>
       </c>
@@ -6553,7 +7091,9 @@
       </c>
     </row>
     <row r="326" spans="1:3">
-      <c r="A326" s="8"/>
+      <c r="A326" s="8">
+        <v>325</v>
+      </c>
       <c r="B326" s="7" t="s">
         <v>393</v>
       </c>
@@ -6562,7 +7102,9 @@
       </c>
     </row>
     <row r="327" spans="1:3">
-      <c r="A327" s="8"/>
+      <c r="A327" s="8">
+        <v>326</v>
+      </c>
       <c r="B327" s="7" t="s">
         <v>394</v>
       </c>
@@ -6571,7 +7113,9 @@
       </c>
     </row>
     <row r="328" spans="1:3">
-      <c r="A328" s="8"/>
+      <c r="A328" s="8">
+        <v>327</v>
+      </c>
       <c r="B328" s="7" t="s">
         <v>395</v>
       </c>
@@ -6580,7 +7124,9 @@
       </c>
     </row>
     <row r="329" spans="1:3">
-      <c r="A329" s="8"/>
+      <c r="A329" s="8">
+        <v>328</v>
+      </c>
       <c r="B329" s="7" t="s">
         <v>396</v>
       </c>
@@ -6589,7 +7135,9 @@
       </c>
     </row>
     <row r="330" spans="1:3">
-      <c r="A330" s="8"/>
+      <c r="A330" s="8">
+        <v>329</v>
+      </c>
       <c r="B330" s="7" t="s">
         <v>397</v>
       </c>
@@ -6598,7 +7146,9 @@
       </c>
     </row>
     <row r="331" spans="1:3">
-      <c r="A331" s="8"/>
+      <c r="A331" s="8">
+        <v>330</v>
+      </c>
       <c r="B331" s="7" t="s">
         <v>398</v>
       </c>
@@ -6607,7 +7157,9 @@
       </c>
     </row>
     <row r="332" spans="1:3">
-      <c r="A332" s="8"/>
+      <c r="A332" s="8">
+        <v>331</v>
+      </c>
       <c r="B332" s="7" t="s">
         <v>399</v>
       </c>
@@ -6616,7 +7168,9 @@
       </c>
     </row>
     <row r="333" spans="1:3">
-      <c r="A333" s="8"/>
+      <c r="A333" s="8">
+        <v>332</v>
+      </c>
       <c r="B333" s="7" t="s">
         <v>400</v>
       </c>
@@ -6625,7 +7179,9 @@
       </c>
     </row>
     <row r="334" spans="1:3">
-      <c r="A334" s="8"/>
+      <c r="A334" s="8">
+        <v>333</v>
+      </c>
       <c r="B334" s="7" t="s">
         <v>401</v>
       </c>
@@ -6634,7 +7190,9 @@
       </c>
     </row>
     <row r="335" spans="1:3">
-      <c r="A335" s="8"/>
+      <c r="A335" s="8">
+        <v>334</v>
+      </c>
       <c r="B335" s="7" t="s">
         <v>402</v>
       </c>
@@ -6643,7 +7201,9 @@
       </c>
     </row>
     <row r="336" spans="1:3">
-      <c r="A336" s="8"/>
+      <c r="A336" s="8">
+        <v>335</v>
+      </c>
       <c r="B336" s="7" t="s">
         <v>403</v>
       </c>
@@ -6652,7 +7212,9 @@
       </c>
     </row>
     <row r="337" spans="1:3">
-      <c r="A337" s="8"/>
+      <c r="A337" s="8">
+        <v>336</v>
+      </c>
       <c r="B337" s="7" t="s">
         <v>404</v>
       </c>
@@ -6661,7 +7223,9 @@
       </c>
     </row>
     <row r="338" spans="1:3">
-      <c r="A338" s="8"/>
+      <c r="A338" s="8">
+        <v>337</v>
+      </c>
       <c r="B338" s="7" t="s">
         <v>405</v>
       </c>
@@ -6670,7 +7234,9 @@
       </c>
     </row>
     <row r="339" spans="1:3">
-      <c r="A339" s="8"/>
+      <c r="A339" s="8">
+        <v>338</v>
+      </c>
       <c r="B339" s="7" t="s">
         <v>406</v>
       </c>
@@ -6679,7 +7245,9 @@
       </c>
     </row>
     <row r="340" spans="1:3">
-      <c r="A340" s="8"/>
+      <c r="A340" s="8">
+        <v>339</v>
+      </c>
       <c r="B340" s="7" t="s">
         <v>407</v>
       </c>
@@ -6688,7 +7256,9 @@
       </c>
     </row>
     <row r="341" spans="1:3">
-      <c r="A341" s="8"/>
+      <c r="A341" s="8">
+        <v>340</v>
+      </c>
       <c r="B341" s="7" t="s">
         <v>408</v>
       </c>
@@ -6697,7 +7267,9 @@
       </c>
     </row>
     <row r="342" spans="1:3">
-      <c r="A342" s="8"/>
+      <c r="A342" s="8">
+        <v>341</v>
+      </c>
       <c r="B342" s="7" t="s">
         <v>409</v>
       </c>
@@ -6706,7 +7278,9 @@
       </c>
     </row>
     <row r="343" spans="1:3">
-      <c r="A343" s="8"/>
+      <c r="A343" s="8">
+        <v>342</v>
+      </c>
       <c r="B343" s="7" t="s">
         <v>410</v>
       </c>
@@ -6715,7 +7289,9 @@
       </c>
     </row>
     <row r="344" spans="1:3">
-      <c r="A344" s="8"/>
+      <c r="A344" s="8">
+        <v>343</v>
+      </c>
       <c r="B344" s="7" t="s">
         <v>411</v>
       </c>
@@ -6724,7 +7300,9 @@
       </c>
     </row>
     <row r="345" spans="1:3">
-      <c r="A345" s="8"/>
+      <c r="A345" s="8">
+        <v>344</v>
+      </c>
       <c r="B345" s="7" t="s">
         <v>412</v>
       </c>
@@ -6733,7 +7311,9 @@
       </c>
     </row>
     <row r="346" spans="1:3">
-      <c r="A346" s="8"/>
+      <c r="A346" s="8">
+        <v>345</v>
+      </c>
       <c r="B346" s="7" t="s">
         <v>413</v>
       </c>
@@ -6742,7 +7322,9 @@
       </c>
     </row>
     <row r="347" spans="1:3">
-      <c r="A347" s="8"/>
+      <c r="A347" s="8">
+        <v>346</v>
+      </c>
       <c r="B347" s="7" t="s">
         <v>414</v>
       </c>
@@ -6751,7 +7333,9 @@
       </c>
     </row>
     <row r="348" spans="1:3">
-      <c r="A348" s="8"/>
+      <c r="A348" s="8">
+        <v>347</v>
+      </c>
       <c r="B348" s="7" t="s">
         <v>415</v>
       </c>
@@ -6760,7 +7344,9 @@
       </c>
     </row>
     <row r="349" spans="1:3">
-      <c r="A349" s="8"/>
+      <c r="A349" s="8">
+        <v>348</v>
+      </c>
       <c r="B349" s="7" t="s">
         <v>416</v>
       </c>
@@ -6769,7 +7355,9 @@
       </c>
     </row>
     <row r="350" spans="1:3">
-      <c r="A350" s="8"/>
+      <c r="A350" s="8">
+        <v>349</v>
+      </c>
       <c r="B350" s="7" t="s">
         <v>417</v>
       </c>
@@ -6778,7 +7366,9 @@
       </c>
     </row>
     <row r="351" spans="1:3">
-      <c r="A351" s="8"/>
+      <c r="A351" s="8">
+        <v>350</v>
+      </c>
       <c r="B351" s="7" t="s">
         <v>418</v>
       </c>
@@ -6787,7 +7377,9 @@
       </c>
     </row>
     <row r="352" spans="1:3">
-      <c r="A352" s="8"/>
+      <c r="A352" s="8">
+        <v>351</v>
+      </c>
       <c r="B352" s="7" t="s">
         <v>419</v>
       </c>
@@ -6796,7 +7388,9 @@
       </c>
     </row>
     <row r="353" spans="1:3">
-      <c r="A353" s="8"/>
+      <c r="A353" s="8">
+        <v>352</v>
+      </c>
       <c r="B353" s="7" t="s">
         <v>420</v>
       </c>
@@ -6805,7 +7399,9 @@
       </c>
     </row>
     <row r="354" spans="1:3">
-      <c r="A354" s="8"/>
+      <c r="A354" s="8">
+        <v>353</v>
+      </c>
       <c r="B354" s="7" t="s">
         <v>421</v>
       </c>
@@ -6814,7 +7410,9 @@
       </c>
     </row>
     <row r="355" spans="1:3">
-      <c r="A355" s="8"/>
+      <c r="A355" s="8">
+        <v>354</v>
+      </c>
       <c r="B355" s="7" t="s">
         <v>422</v>
       </c>
@@ -6823,7 +7421,9 @@
       </c>
     </row>
     <row r="356" spans="1:3">
-      <c r="A356" s="8"/>
+      <c r="A356" s="8">
+        <v>355</v>
+      </c>
       <c r="B356" s="7" t="s">
         <v>423</v>
       </c>
@@ -6832,7 +7432,9 @@
       </c>
     </row>
     <row r="357" spans="1:3">
-      <c r="A357" s="8"/>
+      <c r="A357" s="8">
+        <v>356</v>
+      </c>
       <c r="B357" s="7" t="s">
         <v>424</v>
       </c>
@@ -6841,7 +7443,9 @@
       </c>
     </row>
     <row r="358" spans="1:3">
-      <c r="A358" s="8"/>
+      <c r="A358" s="8">
+        <v>357</v>
+      </c>
       <c r="B358" s="7" t="s">
         <v>425</v>
       </c>
@@ -6850,7 +7454,9 @@
       </c>
     </row>
     <row r="359" spans="1:3">
-      <c r="A359" s="8"/>
+      <c r="A359" s="8">
+        <v>358</v>
+      </c>
       <c r="B359" s="7" t="s">
         <v>426</v>
       </c>
@@ -6859,7 +7465,9 @@
       </c>
     </row>
     <row r="360" spans="1:3">
-      <c r="A360" s="8"/>
+      <c r="A360" s="8">
+        <v>359</v>
+      </c>
       <c r="B360" s="7" t="s">
         <v>427</v>
       </c>
@@ -6868,7 +7476,9 @@
       </c>
     </row>
     <row r="361" spans="1:3">
-      <c r="A361" s="8"/>
+      <c r="A361" s="8">
+        <v>360</v>
+      </c>
       <c r="B361" s="7" t="s">
         <v>428</v>
       </c>
@@ -6877,7 +7487,9 @@
       </c>
     </row>
     <row r="362" spans="1:3">
-      <c r="A362" s="8"/>
+      <c r="A362" s="8">
+        <v>361</v>
+      </c>
       <c r="B362" s="7" t="s">
         <v>429</v>
       </c>
@@ -6886,7 +7498,9 @@
       </c>
     </row>
     <row r="363" spans="1:3">
-      <c r="A363" s="8"/>
+      <c r="A363" s="8">
+        <v>362</v>
+      </c>
       <c r="B363" s="7" t="s">
         <v>430</v>
       </c>
@@ -6895,7 +7509,9 @@
       </c>
     </row>
     <row r="364" spans="1:3">
-      <c r="A364" s="8"/>
+      <c r="A364" s="8">
+        <v>363</v>
+      </c>
       <c r="B364" s="7" t="s">
         <v>431</v>
       </c>
@@ -6904,7 +7520,9 @@
       </c>
     </row>
     <row r="365" spans="1:3">
-      <c r="A365" s="8"/>
+      <c r="A365" s="8">
+        <v>364</v>
+      </c>
       <c r="B365" s="7" t="s">
         <v>432</v>
       </c>
@@ -6913,7 +7531,9 @@
       </c>
     </row>
     <row r="366" spans="1:3">
-      <c r="A366" s="8"/>
+      <c r="A366" s="8">
+        <v>365</v>
+      </c>
       <c r="B366" s="7" t="s">
         <v>433</v>
       </c>
@@ -6922,7 +7542,9 @@
       </c>
     </row>
     <row r="367" spans="1:3">
-      <c r="A367" s="8"/>
+      <c r="A367" s="8">
+        <v>366</v>
+      </c>
       <c r="B367" s="7" t="s">
         <v>434</v>
       </c>
@@ -6931,7 +7553,9 @@
       </c>
     </row>
     <row r="368" spans="1:3">
-      <c r="A368" s="8"/>
+      <c r="A368" s="8">
+        <v>367</v>
+      </c>
       <c r="B368" s="7" t="s">
         <v>435</v>
       </c>
@@ -6940,7 +7564,9 @@
       </c>
     </row>
     <row r="369" spans="1:3">
-      <c r="A369" s="8"/>
+      <c r="A369" s="8">
+        <v>368</v>
+      </c>
       <c r="B369" s="7" t="s">
         <v>436</v>
       </c>
@@ -6949,7 +7575,9 @@
       </c>
     </row>
     <row r="370" spans="1:3">
-      <c r="A370" s="8"/>
+      <c r="A370" s="8">
+        <v>369</v>
+      </c>
       <c r="B370" s="7" t="s">
         <v>437</v>
       </c>
@@ -6958,7 +7586,9 @@
       </c>
     </row>
     <row r="371" spans="1:3">
-      <c r="A371" s="8"/>
+      <c r="A371" s="8">
+        <v>370</v>
+      </c>
       <c r="B371" s="7" t="s">
         <v>438</v>
       </c>
@@ -6967,7 +7597,9 @@
       </c>
     </row>
     <row r="372" spans="1:3">
-      <c r="A372" s="8"/>
+      <c r="A372" s="8">
+        <v>371</v>
+      </c>
       <c r="B372" s="7" t="s">
         <v>439</v>
       </c>
@@ -6976,7 +7608,9 @@
       </c>
     </row>
     <row r="373" spans="1:3">
-      <c r="A373" s="8"/>
+      <c r="A373" s="8">
+        <v>372</v>
+      </c>
       <c r="B373" s="7" t="s">
         <v>440</v>
       </c>
@@ -6985,7 +7619,9 @@
       </c>
     </row>
     <row r="374" spans="1:3">
-      <c r="A374" s="8"/>
+      <c r="A374" s="8">
+        <v>373</v>
+      </c>
       <c r="B374" s="7" t="s">
         <v>441</v>
       </c>
@@ -6994,7 +7630,9 @@
       </c>
     </row>
     <row r="375" spans="1:3">
-      <c r="A375" s="8"/>
+      <c r="A375" s="8">
+        <v>374</v>
+      </c>
       <c r="B375" s="7" t="s">
         <v>442</v>
       </c>
@@ -7003,7 +7641,9 @@
       </c>
     </row>
     <row r="376" spans="1:3">
-      <c r="A376" s="8"/>
+      <c r="A376" s="8">
+        <v>375</v>
+      </c>
       <c r="B376" s="7" t="s">
         <v>443</v>
       </c>
@@ -7012,7 +7652,9 @@
       </c>
     </row>
     <row r="377" spans="1:3">
-      <c r="A377" s="8"/>
+      <c r="A377" s="8">
+        <v>376</v>
+      </c>
       <c r="B377" s="7" t="s">
         <v>444</v>
       </c>
@@ -7021,7 +7663,9 @@
       </c>
     </row>
     <row r="378" spans="1:3">
-      <c r="A378" s="8"/>
+      <c r="A378" s="8">
+        <v>377</v>
+      </c>
       <c r="B378" s="7" t="s">
         <v>445</v>
       </c>
@@ -7030,7 +7674,9 @@
       </c>
     </row>
     <row r="379" spans="1:3">
-      <c r="A379" s="8"/>
+      <c r="A379" s="8">
+        <v>378</v>
+      </c>
       <c r="B379" s="7" t="s">
         <v>446</v>
       </c>
@@ -7039,7 +7685,9 @@
       </c>
     </row>
     <row r="380" spans="1:3">
-      <c r="A380" s="8"/>
+      <c r="A380" s="8">
+        <v>379</v>
+      </c>
       <c r="B380" s="7" t="s">
         <v>447</v>
       </c>
@@ -7048,7 +7696,9 @@
       </c>
     </row>
     <row r="381" spans="1:3">
-      <c r="A381" s="8"/>
+      <c r="A381" s="8">
+        <v>380</v>
+      </c>
       <c r="B381" s="7" t="s">
         <v>448</v>
       </c>
@@ -7057,7 +7707,9 @@
       </c>
     </row>
     <row r="382" spans="1:3">
-      <c r="A382" s="8"/>
+      <c r="A382" s="8">
+        <v>381</v>
+      </c>
       <c r="B382" s="7" t="s">
         <v>449</v>
       </c>
@@ -7066,7 +7718,9 @@
       </c>
     </row>
     <row r="383" spans="1:3">
-      <c r="A383" s="8"/>
+      <c r="A383" s="8">
+        <v>382</v>
+      </c>
       <c r="B383" s="7" t="s">
         <v>450</v>
       </c>
@@ -7075,7 +7729,9 @@
       </c>
     </row>
     <row r="384" spans="1:3">
-      <c r="A384" s="8"/>
+      <c r="A384" s="8">
+        <v>383</v>
+      </c>
       <c r="B384" s="7" t="s">
         <v>451</v>
       </c>
@@ -7084,7 +7740,9 @@
       </c>
     </row>
     <row r="385" spans="1:3">
-      <c r="A385" s="8"/>
+      <c r="A385" s="8">
+        <v>384</v>
+      </c>
       <c r="B385" s="7" t="s">
         <v>452</v>
       </c>
@@ -7093,7 +7751,9 @@
       </c>
     </row>
     <row r="386" spans="1:3">
-      <c r="A386" s="8"/>
+      <c r="A386" s="8">
+        <v>385</v>
+      </c>
       <c r="B386" s="7" t="s">
         <v>453</v>
       </c>
@@ -7102,7 +7762,9 @@
       </c>
     </row>
     <row r="387" spans="1:3">
-      <c r="A387" s="8"/>
+      <c r="A387" s="8">
+        <v>386</v>
+      </c>
       <c r="B387" s="7" t="s">
         <v>454</v>
       </c>
@@ -7111,7 +7773,9 @@
       </c>
     </row>
     <row r="388" spans="1:3">
-      <c r="A388" s="8"/>
+      <c r="A388" s="8">
+        <v>387</v>
+      </c>
       <c r="B388" s="7" t="s">
         <v>455</v>
       </c>
@@ -7120,7 +7784,9 @@
       </c>
     </row>
     <row r="389" spans="1:3">
-      <c r="A389" s="8"/>
+      <c r="A389" s="8">
+        <v>388</v>
+      </c>
       <c r="B389" s="7" t="s">
         <v>456</v>
       </c>
@@ -7129,7 +7795,9 @@
       </c>
     </row>
     <row r="390" spans="1:3">
-      <c r="A390" s="8"/>
+      <c r="A390" s="8">
+        <v>389</v>
+      </c>
       <c r="B390" s="7" t="s">
         <v>457</v>
       </c>
@@ -7138,7 +7806,9 @@
       </c>
     </row>
     <row r="391" spans="1:3">
-      <c r="A391" s="8"/>
+      <c r="A391" s="8">
+        <v>390</v>
+      </c>
       <c r="B391" s="7" t="s">
         <v>458</v>
       </c>
@@ -7147,7 +7817,9 @@
       </c>
     </row>
     <row r="392" spans="1:3">
-      <c r="A392" s="8"/>
+      <c r="A392" s="8">
+        <v>391</v>
+      </c>
       <c r="B392" s="7" t="s">
         <v>459</v>
       </c>
@@ -7156,7 +7828,9 @@
       </c>
     </row>
     <row r="393" spans="1:3">
-      <c r="A393" s="8"/>
+      <c r="A393" s="8">
+        <v>392</v>
+      </c>
       <c r="B393" s="7" t="s">
         <v>460</v>
       </c>
@@ -7165,7 +7839,9 @@
       </c>
     </row>
     <row r="394" spans="1:3">
-      <c r="A394" s="8"/>
+      <c r="A394" s="8">
+        <v>393</v>
+      </c>
       <c r="B394" s="7" t="s">
         <v>461</v>
       </c>
@@ -7174,7 +7850,9 @@
       </c>
     </row>
     <row r="395" spans="1:3">
-      <c r="A395" s="8"/>
+      <c r="A395" s="8">
+        <v>394</v>
+      </c>
       <c r="B395" s="7" t="s">
         <v>462</v>
       </c>
@@ -7183,7 +7861,9 @@
       </c>
     </row>
     <row r="396" spans="1:3">
-      <c r="A396" s="8"/>
+      <c r="A396" s="8">
+        <v>395</v>
+      </c>
       <c r="B396" s="7" t="s">
         <v>463</v>
       </c>
@@ -7192,7 +7872,9 @@
       </c>
     </row>
     <row r="397" spans="1:3">
-      <c r="A397" s="8"/>
+      <c r="A397" s="8">
+        <v>396</v>
+      </c>
       <c r="B397" s="7" t="s">
         <v>464</v>
       </c>
@@ -7201,7 +7883,9 @@
       </c>
     </row>
     <row r="398" spans="1:3">
-      <c r="A398" s="8"/>
+      <c r="A398" s="8">
+        <v>397</v>
+      </c>
       <c r="B398" s="7" t="s">
         <v>465</v>
       </c>
@@ -7210,7 +7894,9 @@
       </c>
     </row>
     <row r="399" spans="1:3">
-      <c r="A399" s="8"/>
+      <c r="A399" s="8">
+        <v>398</v>
+      </c>
       <c r="B399" s="7" t="s">
         <v>466</v>
       </c>
@@ -7219,7 +7905,9 @@
       </c>
     </row>
     <row r="400" spans="1:3">
-      <c r="A400" s="8"/>
+      <c r="A400" s="8">
+        <v>399</v>
+      </c>
       <c r="B400" s="7" t="s">
         <v>467</v>
       </c>
@@ -7228,7 +7916,9 @@
       </c>
     </row>
     <row r="401" spans="1:3">
-      <c r="A401" s="8"/>
+      <c r="A401" s="8">
+        <v>400</v>
+      </c>
       <c r="B401" s="7" t="s">
         <v>468</v>
       </c>
@@ -7237,7 +7927,9 @@
       </c>
     </row>
     <row r="402" spans="1:3">
-      <c r="A402" s="8"/>
+      <c r="A402" s="8">
+        <v>401</v>
+      </c>
       <c r="B402" s="7" t="s">
         <v>469</v>
       </c>
@@ -7246,7 +7938,9 @@
       </c>
     </row>
     <row r="403" spans="1:3">
-      <c r="A403" s="8"/>
+      <c r="A403" s="8">
+        <v>402</v>
+      </c>
       <c r="B403" s="7" t="s">
         <v>470</v>
       </c>
@@ -7255,7 +7949,9 @@
       </c>
     </row>
     <row r="404" spans="1:3">
-      <c r="A404" s="8"/>
+      <c r="A404" s="8">
+        <v>403</v>
+      </c>
       <c r="B404" s="7" t="s">
         <v>471</v>
       </c>
@@ -7264,7 +7960,9 @@
       </c>
     </row>
     <row r="405" spans="1:3">
-      <c r="A405" s="8"/>
+      <c r="A405" s="8">
+        <v>404</v>
+      </c>
       <c r="B405" s="7" t="s">
         <v>472</v>
       </c>
@@ -7273,7 +7971,9 @@
       </c>
     </row>
     <row r="406" spans="1:3">
-      <c r="A406" s="8"/>
+      <c r="A406" s="8">
+        <v>405</v>
+      </c>
       <c r="B406" s="7" t="s">
         <v>473</v>
       </c>
@@ -7282,7 +7982,9 @@
       </c>
     </row>
     <row r="407" spans="1:3">
-      <c r="A407" s="8"/>
+      <c r="A407" s="8">
+        <v>406</v>
+      </c>
       <c r="B407" s="7" t="s">
         <v>474</v>
       </c>
@@ -7291,7 +7993,9 @@
       </c>
     </row>
     <row r="408" spans="1:3">
-      <c r="A408" s="8"/>
+      <c r="A408" s="8">
+        <v>407</v>
+      </c>
       <c r="B408" s="7" t="s">
         <v>475</v>
       </c>
@@ -7300,7 +8004,9 @@
       </c>
     </row>
     <row r="409" spans="1:3">
-      <c r="A409" s="8"/>
+      <c r="A409" s="8">
+        <v>408</v>
+      </c>
       <c r="B409" s="7" t="s">
         <v>476</v>
       </c>
@@ -7309,7 +8015,9 @@
       </c>
     </row>
     <row r="410" spans="1:3">
-      <c r="A410" s="8"/>
+      <c r="A410" s="8">
+        <v>409</v>
+      </c>
       <c r="B410" s="7" t="s">
         <v>477</v>
       </c>
@@ -7318,7 +8026,9 @@
       </c>
     </row>
     <row r="411" spans="1:3">
-      <c r="A411" s="8"/>
+      <c r="A411" s="8">
+        <v>410</v>
+      </c>
       <c r="B411" s="7" t="s">
         <v>478</v>
       </c>
@@ -7327,7 +8037,9 @@
       </c>
     </row>
     <row r="412" spans="1:3">
-      <c r="A412" s="8"/>
+      <c r="A412" s="8">
+        <v>411</v>
+      </c>
       <c r="B412" s="7" t="s">
         <v>479</v>
       </c>
@@ -7336,7 +8048,9 @@
       </c>
     </row>
     <row r="413" spans="1:3">
-      <c r="A413" s="8"/>
+      <c r="A413" s="8">
+        <v>412</v>
+      </c>
       <c r="B413" s="7" t="s">
         <v>480</v>
       </c>
@@ -7345,7 +8059,9 @@
       </c>
     </row>
     <row r="414" spans="1:3">
-      <c r="A414" s="8"/>
+      <c r="A414" s="8">
+        <v>413</v>
+      </c>
       <c r="B414" s="7" t="s">
         <v>481</v>
       </c>
@@ -7354,7 +8070,9 @@
       </c>
     </row>
     <row r="415" spans="1:3">
-      <c r="A415" s="8"/>
+      <c r="A415" s="8">
+        <v>414</v>
+      </c>
       <c r="B415" s="7" t="s">
         <v>482</v>
       </c>
@@ -7363,7 +8081,9 @@
       </c>
     </row>
     <row r="416" spans="1:3">
-      <c r="A416" s="8"/>
+      <c r="A416" s="8">
+        <v>415</v>
+      </c>
       <c r="B416" s="7" t="s">
         <v>483</v>
       </c>
@@ -7372,7 +8092,9 @@
       </c>
     </row>
     <row r="417" spans="1:3">
-      <c r="A417" s="8"/>
+      <c r="A417" s="8">
+        <v>416</v>
+      </c>
       <c r="B417" s="7" t="s">
         <v>484</v>
       </c>
@@ -7381,7 +8103,9 @@
       </c>
     </row>
     <row r="418" spans="1:3">
-      <c r="A418" s="8"/>
+      <c r="A418" s="8">
+        <v>417</v>
+      </c>
       <c r="B418" s="7" t="s">
         <v>485</v>
       </c>
@@ -7390,7 +8114,9 @@
       </c>
     </row>
     <row r="419" spans="1:3">
-      <c r="A419" s="8"/>
+      <c r="A419" s="8">
+        <v>418</v>
+      </c>
       <c r="B419" s="7" t="s">
         <v>486</v>
       </c>
@@ -7399,7 +8125,9 @@
       </c>
     </row>
     <row r="420" spans="1:3">
-      <c r="A420" s="8"/>
+      <c r="A420" s="8">
+        <v>419</v>
+      </c>
       <c r="B420" s="7" t="s">
         <v>487</v>
       </c>
@@ -7408,7 +8136,9 @@
       </c>
     </row>
     <row r="421" spans="1:3">
-      <c r="A421" s="8"/>
+      <c r="A421" s="8">
+        <v>420</v>
+      </c>
       <c r="B421" s="7" t="s">
         <v>488</v>
       </c>
@@ -7417,7 +8147,9 @@
       </c>
     </row>
     <row r="422" spans="1:3">
-      <c r="A422" s="8"/>
+      <c r="A422" s="8">
+        <v>421</v>
+      </c>
       <c r="B422" s="7" t="s">
         <v>489</v>
       </c>
@@ -7426,7 +8158,9 @@
       </c>
     </row>
     <row r="423" spans="1:3">
-      <c r="A423" s="8"/>
+      <c r="A423" s="8">
+        <v>422</v>
+      </c>
       <c r="B423" s="7" t="s">
         <v>490</v>
       </c>
@@ -7435,7 +8169,9 @@
       </c>
     </row>
     <row r="424" spans="1:3">
-      <c r="A424" s="8"/>
+      <c r="A424" s="8">
+        <v>423</v>
+      </c>
       <c r="B424" s="7" t="s">
         <v>491</v>
       </c>
@@ -7444,7 +8180,9 @@
       </c>
     </row>
     <row r="425" spans="1:3">
-      <c r="A425" s="8"/>
+      <c r="A425" s="8">
+        <v>424</v>
+      </c>
       <c r="B425" s="7" t="s">
         <v>492</v>
       </c>
@@ -7453,7 +8191,9 @@
       </c>
     </row>
     <row r="426" spans="1:3">
-      <c r="A426" s="8"/>
+      <c r="A426" s="8">
+        <v>425</v>
+      </c>
       <c r="B426" s="7" t="s">
         <v>493</v>
       </c>
@@ -7462,7 +8202,9 @@
       </c>
     </row>
     <row r="427" spans="1:3">
-      <c r="A427" s="8"/>
+      <c r="A427" s="8">
+        <v>426</v>
+      </c>
       <c r="B427" s="7" t="s">
         <v>494</v>
       </c>
@@ -7471,7 +8213,9 @@
       </c>
     </row>
     <row r="428" spans="1:3">
-      <c r="A428" s="8"/>
+      <c r="A428" s="8">
+        <v>427</v>
+      </c>
       <c r="B428" s="7" t="s">
         <v>495</v>
       </c>
@@ -7480,7 +8224,9 @@
       </c>
     </row>
     <row r="429" spans="1:3">
-      <c r="A429" s="8"/>
+      <c r="A429" s="8">
+        <v>428</v>
+      </c>
       <c r="B429" s="7" t="s">
         <v>496</v>
       </c>
@@ -7489,7 +8235,9 @@
       </c>
     </row>
     <row r="430" spans="1:3">
-      <c r="A430" s="8"/>
+      <c r="A430" s="8">
+        <v>429</v>
+      </c>
       <c r="B430" s="7" t="s">
         <v>497</v>
       </c>
@@ -7498,7 +8246,9 @@
       </c>
     </row>
     <row r="431" spans="1:3">
-      <c r="A431" s="8"/>
+      <c r="A431" s="8">
+        <v>430</v>
+      </c>
       <c r="B431" s="7" t="s">
         <v>498</v>
       </c>
@@ -7507,7 +8257,9 @@
       </c>
     </row>
     <row r="432" spans="1:3">
-      <c r="A432" s="8"/>
+      <c r="A432" s="8">
+        <v>431</v>
+      </c>
       <c r="B432" s="7" t="s">
         <v>499</v>
       </c>
@@ -7516,7 +8268,9 @@
       </c>
     </row>
     <row r="433" spans="1:3">
-      <c r="A433" s="8"/>
+      <c r="A433" s="8">
+        <v>432</v>
+      </c>
       <c r="B433" s="7" t="s">
         <v>500</v>
       </c>
@@ -7525,7 +8279,9 @@
       </c>
     </row>
     <row r="434" spans="1:3">
-      <c r="A434" s="8"/>
+      <c r="A434" s="8">
+        <v>433</v>
+      </c>
       <c r="B434" s="7" t="s">
         <v>501</v>
       </c>

--- a/CopadoMundoFIFA2026_DadosPowerBI.xlsx
+++ b/CopadoMundoFIFA2026_DadosPowerBI.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30327"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9018FC1F-37E8-48A7-AE67-7BE5CF9C2266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D8B8665-F9BC-47A3-B50E-10055E8B3A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="4" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DimSelecao" sheetId="1" r:id="rId1"/>
@@ -11706,7 +11706,7 @@
         <v>577</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45">
         <v>2</v>
